--- a/docs/weekly/SLATE_FULL_2026_W07.xlsx
+++ b/docs/weekly/SLATE_FULL_2026_W07.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Parlays across the slate (fa" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 This league (SPAMML) view" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Last week's scorecard (Week " sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Known gaps and audit results" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10b Lines with no projection, a" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Known gaps and audit results" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +486,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T01:46:37Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T01:35:01+00:00. nflverse injuries and depth charts: latest published (no timestamp in the feed). Lines: ESPN/DraftKings (no prices). Official inactives: not used (about 90 minutes before each kickoff).</t>
+          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T12:01:29Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T12:01:26+00:00. nflverse depth charts: 2026-10-25T06:01:49Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T12:10Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git c21ee9a.</t>
         </is>
       </c>
     </row>
@@ -569,77 +570,77 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.718</v>
+        <v>0.723</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.715</v>
+        <v>0.722</v>
       </c>
       <c r="D8" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E8" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.715</v>
+        <v>0.722</v>
       </c>
       <c r="D9" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E9" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.448</v>
+        <v>0.455</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.7040000000000001</v>
+        <v>0.721</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11"/>
@@ -703,54 +704,54 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.369</v>
+        <v>0.3720000000000001</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.503</v>
+        <v>0.51</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E15" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>NYG@HOU: Woody Marks anytime TD + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.501</v>
+        <v>0.509</v>
       </c>
       <c r="D16" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E16" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks anytime TD + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>NYG@HOU: Woody Marks anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.501</v>
+        <v>0.507</v>
       </c>
       <c r="D17" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E17" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18"/>
@@ -798,77 +799,77 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.293</v>
+        <v>0.304</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.602</v>
       </c>
       <c r="D22" t="n">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E22" t="n">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.292</v>
+        <v>0.303</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.601</v>
       </c>
       <c r="D23" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E23" t="n">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.292</v>
+        <v>0.303</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.599</v>
       </c>
       <c r="D24" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E24" t="n">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jared Goff pass TD 1+</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="D25" t="n">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="E25" t="n">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26"/>
@@ -909,64 +910,64 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.272</v>
+        <v>0.273</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0.451</v>
+        <v>0.454</v>
       </c>
       <c r="D29" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E29" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.265</v>
+        <v>0.273</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.431</v>
+        <v>0.454</v>
       </c>
       <c r="D30" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="E30" t="n">
-        <v>323</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.261</v>
+        <v>0.266</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0.422</v>
+        <v>0.433</v>
       </c>
       <c r="D31" t="n">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="E31" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEN@ARI: Jacoby Brissett rush_yds O6.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -1027,77 +1028,77 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + DAL@PHI: Javonte Williams rush_att U16.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.187</v>
+        <v>0.197</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.44</v>
+        <v>0.479</v>
       </c>
       <c r="D37" t="n">
-        <v>436</v>
+        <v>408</v>
       </c>
       <c r="E37" t="n">
-        <v>500</v>
+        <v>469</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + CIN@BAL: Samaje Perine rush_att U7.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.187</v>
+        <v>0.196</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.478</v>
       </c>
       <c r="D38" t="n">
-        <v>436</v>
+        <v>409</v>
       </c>
       <c r="E38" t="n">
-        <v>500</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + DEN@ARI: Jacoby Brissett rush_yds O6.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.186</v>
+        <v>0.196</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.476</v>
       </c>
       <c r="D39" t="n">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="E39" t="n">
-        <v>501</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jared Goff pass TD 1+</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>0.186</v>
+        <v>0.195</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.472</v>
       </c>
       <c r="D40" t="n">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="E40" t="n">
-        <v>501</v>
+        <v>474</v>
       </c>
     </row>
     <row r="41"/>
@@ -1138,77 +1139,77 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>0.176</v>
+        <v>0.182</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.357</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="E44" t="n">
-        <v>537</v>
+        <v>515</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>0.174</v>
+        <v>0.177</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.35</v>
+        <v>0.361</v>
       </c>
       <c r="D45" t="n">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="E45" t="n">
-        <v>545</v>
+        <v>533</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Jacoby Brissett rush_yds O6.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>0.173</v>
+        <v>0.177</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>0.349</v>
+        <v>0.361</v>
       </c>
       <c r="D46" t="n">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="E46" t="n">
-        <v>546</v>
+        <v>533</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.172</v>
+        <v>0.174</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="D47" t="n">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E47" t="n">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48"/>
@@ -1256,19 +1257,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>59% (55%)</t>
+          <t>61% (55%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Matthew Stafford</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>86% (68%)</t>
+          <t>87% (68%)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1280,7 +1281,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Matthew Stafford</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1290,7 +1291,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>57% (53%)</t>
+          <t>57% (54%)</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1303,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>85% (68%)</t>
+          <t>86% (68%)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>55% (52%)</t>
+          <t>55% (53%)</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1332,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1341,7 +1342,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>49% (49%)</t>
+          <t>50% (50%)</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1366,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1382,24 +1383,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>80% (65%)</t>
+          <t>81% (65%)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>48% (49%)</t>
+          <t>47% (48%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1409,7 +1410,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>47% (48%)</t>
+          <t>48% (49%)</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1451,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1467,7 +1468,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1535,7 +1536,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1545,19 +1546,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30% (40%)</t>
+          <t>29% (40%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>67% (58%)</t>
+          <t>67% (59%)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1574,7 +1575,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>66% (58%)</t>
+          <t>67% (58%)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1608,7 +1609,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>46% (48%)</t>
+          <t>45% (47%)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1813,6 +1814,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="57" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>10b. Lines with no projection, and players withheld</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>4 players have posted lines but no projection row (not on the 2026 stats universe, injured/exempt, or name mismatch). Nothing is published for them:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Christian Kirk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SF@ATL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>reception_yds, receptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GB@DET</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>reception_yds, receptions, rush_attempts, rush_yds</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Khalil Herbert</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SF@ATL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>rush_yds</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Tank Dell</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NYG@HOU</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>reception_yds, receptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Withheld on purpose (no line, touchdown or parlay leg):</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Josh Jacobs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RB1 on the depth chart and ACT on the roster with no 2026 games and no projection row (book lines posted; role unknown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GB backfield shares are unpriced while Jacobs is missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kaleb Johnson</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GB backfield shares are unpriced while Jacobs is missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pierre Strong</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GB backfield shares are unpriced while Jacobs is missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GB backfield shares are unpriced while Jacobs is missing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1830,7 +2086,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Three agents (data audit, model sanity, red-team) reviewed this run before it was frozen. Each window is audited before it is frozen (QB1 against the depth chart, bye-team rows, Out players and their volume, team codes, unmatched names); the verdicts are in the run notes of the frozen manifest. Remaining, by how much they change a pick:</t>
+          <t>Each window is audited before it is frozen by a data audit, a model sanity check and a red-team pass (QB1 against the depth chart, bye-team rows, Out players and their volume, team codes, unmatched names); the audit verdicts are written into the run notes of the frozen manifest. Remaining, by how much they change a pick:</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2264,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PIT 24.6, NO 22.3</t>
+          <t>PIT 24.6, NO 22.2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PIT 57%</t>
+          <t>PIT 56%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2085,7 +2341,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CIN 24.7, BAL 21.7</t>
+          <t>CIN 24.8, BAL 21.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2098,7 +2354,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CIN 23.7, BAL 26.4</t>
+          <t>CIN 23.6, BAL 26.4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2130,7 +2386,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TB 20.8, CAR 23.8</t>
+          <t>TB 20.7, CAR 23.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2170,17 +2426,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOU -10.0 / 42.5</t>
+          <t>HOU -10.5 / 42.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NYG 16.3, HOU 26.1</t>
+          <t>NYG 16.0, HOU 26.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NYG 23% / HOU 77%</t>
+          <t>NYG 21% / HOU 79%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2193,7 +2449,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NYG 34%</t>
+          <t>NYG 35%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2220,7 +2476,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IND 17.4, MIN 24.0</t>
+          <t>IND 17.4, MIN 24.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2265,7 +2521,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIA 17.5, NYJ 21.9</t>
+          <t>MIA 17.4, NYJ 22.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2278,12 +2534,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MIA 18.7, NYJ 22.0</t>
+          <t>MIA 18.8, NYJ 22.1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MIA 41%</t>
+          <t>MIA 40%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2305,17 +2561,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TEN +2.5 / 36.5</t>
+          <t>TEN +1.5 / 36.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE 19.3, TEN 17.0</t>
+          <t>CLE 18.9, TEN 17.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE 57% / TEN 43%</t>
+          <t>CLE 54% / TEN 46%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2323,7 +2579,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CLE 19.0, TEN 17.6</t>
+          <t>CLE 19.1, TEN 17.8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2333,7 +2589,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TEN +3.0</t>
+          <t>TEN +1.0</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2611,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DEN 23.9, ARI 19.4</t>
+          <t>DEN 24.0, ARI 19.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2364,16 +2620,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DEN 23.4, ARI 21.1</t>
+          <t>DEN 23.3, ARI 21.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DEN 57%</t>
+          <t>DEN 56%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2395,12 +2651,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DET -3.5 / 54.5</t>
+          <t>DET -3.5 / 55.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GB 25.4, DET 29.0</t>
+          <t>GB 26.0, DET 29.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2409,11 +2665,11 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54.4</v>
+        <v>55.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GB 22.7, DET 27.8</t>
+          <t>GB 22.8, DET 27.9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2423,7 +2679,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DET -4.0</t>
+          <t>DET -3.0</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2701,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA 25.7, LV 22.7</t>
+          <t>LA 25.7, LV 22.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2454,16 +2710,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>48.4</v>
+        <v>48.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LA 24.9, LV 23.1</t>
+          <t>LA 24.8, LV 23.3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LA 56%</t>
+          <t>LA 55%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2490,20 +2746,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KC 19.8, SEA 22.7</t>
+          <t>KC 19.7, SEA 22.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC 41% / SEA 59%</t>
+          <t>KC 42% / SEA 58%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KC 21.7, SEA 24.2</t>
+          <t>KC 21.6, SEA 24.2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2535,25 +2791,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DAL 23.9, PHI 19.5</t>
+          <t>DAL 24.1, PHI 19.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DAL 62% / PHI 38%</t>
+          <t>DAL 63% / PHI 37%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DAL 23.3, PHI 23.9</t>
+          <t>DAL 23.1, PHI 23.9</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DAL 48%</t>
+          <t>DAL 47%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -8150,10 +8406,10 @@
         <v>22.9</v>
       </c>
       <c r="F7" t="n">
-        <v>289.4</v>
+        <v>288.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
@@ -8165,10 +8421,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>11.8</v>
+        <v>12.1</v>
       </c>
       <c r="L7" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="8">
@@ -8191,13 +8447,13 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="F8" t="n">
-        <v>258.2</v>
+        <v>257.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="H8" t="n">
         <v>3.4</v>
@@ -8238,10 +8494,10 @@
         <v>22.2</v>
       </c>
       <c r="F9" t="n">
-        <v>231.1</v>
+        <v>230</v>
       </c>
       <c r="G9" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H9" t="n">
         <v>4.8</v>
@@ -8253,10 +8509,10 @@
         <v>0.11</v>
       </c>
       <c r="K9" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="L9" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="10">
@@ -8279,28 +8535,28 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="F10" t="n">
-        <v>239.9</v>
+        <v>238.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="K10" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="L10" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
     </row>
     <row r="11">
@@ -8326,10 +8582,10 @@
         <v>23.3</v>
       </c>
       <c r="F11" t="n">
-        <v>244.2</v>
+        <v>244.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H11" t="n">
         <v>8</v>
@@ -8341,7 +8597,7 @@
         <v>0.11</v>
       </c>
       <c r="K11" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="L11" t="n">
         <v>16.4</v>
@@ -8370,25 +8626,25 @@
         <v>18.6</v>
       </c>
       <c r="F12" t="n">
-        <v>212.9</v>
+        <v>212.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="K12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="L12" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="13">
@@ -8414,7 +8670,7 @@
         <v>21.5</v>
       </c>
       <c r="F13" t="n">
-        <v>252.3</v>
+        <v>252.5</v>
       </c>
       <c r="G13" t="n">
         <v>1.6</v>
@@ -8423,16 +8679,16 @@
         <v>8.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="K13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="L13" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="14">
@@ -8458,7 +8714,7 @@
         <v>20.4</v>
       </c>
       <c r="F14" t="n">
-        <v>225.9</v>
+        <v>225.6</v>
       </c>
       <c r="G14" t="n">
         <v>1.58</v>
@@ -8526,89 +8782,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>16.6</v>
+        <v>23.9</v>
       </c>
       <c r="F16" t="n">
-        <v>192.4</v>
+        <v>258.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="H16" t="n">
-        <v>20.6</v>
+        <v>8.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="K16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>23.9</v>
+        <v>16.7</v>
       </c>
       <c r="F17" t="n">
-        <v>257.7</v>
+        <v>190.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>14.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="K17" t="n">
         <v>9.1</v>
       </c>
       <c r="L17" t="n">
-        <v>15.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="18">
@@ -8631,16 +8887,16 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="F18" t="n">
-        <v>200</v>
+        <v>197.5</v>
       </c>
       <c r="G18" t="n">
         <v>1.4</v>
       </c>
       <c r="H18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I18" t="n">
         <v>0.09</v>
@@ -8652,7 +8908,7 @@
         <v>8.9</v>
       </c>
       <c r="L18" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="19">
@@ -8678,13 +8934,13 @@
         <v>19.2</v>
       </c>
       <c r="F19" t="n">
-        <v>216.3</v>
+        <v>217</v>
       </c>
       <c r="G19" t="n">
         <v>1.41</v>
       </c>
       <c r="H19" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I19" t="n">
         <v>0.07000000000000001</v>
@@ -8696,7 +8952,7 @@
         <v>8.9</v>
       </c>
       <c r="L19" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="20"/>
@@ -8802,31 +9058,31 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>91.7</v>
+        <v>91.8</v>
       </c>
       <c r="G23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="H23" t="n">
         <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="J23" t="n">
         <v>0.21</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M23" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N23" t="n">
         <v>24.6</v>
-      </c>
-      <c r="N23" t="n">
-        <v>24.4</v>
       </c>
     </row>
     <row r="24">
@@ -8902,16 +9158,16 @@
         <v>20.6</v>
       </c>
       <c r="F25" t="n">
-        <v>102.3</v>
+        <v>101.4</v>
       </c>
       <c r="G25" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
         <v>0.19</v>
@@ -8923,10 +9179,10 @@
         <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="N25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="26">
@@ -8952,7 +9208,7 @@
         <v>13.4</v>
       </c>
       <c r="F26" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="G26" t="n">
         <v>0.63</v>
@@ -9002,7 +9258,7 @@
         <v>13.7</v>
       </c>
       <c r="F27" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="G27" t="n">
         <v>0.77</v>
@@ -9011,22 +9267,22 @@
         <v>2.7</v>
       </c>
       <c r="I27" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="L27" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="M27" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="N27" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
@@ -9052,131 +9308,131 @@
         <v>18.6</v>
       </c>
       <c r="F28" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="H28" t="n">
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="J28" t="n">
         <v>0.1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M28" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N28" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>18.6</v>
+        <v>15.4</v>
       </c>
       <c r="F29" t="n">
-        <v>97.2</v>
+        <v>58.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>24.1</v>
+        <v>26.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="L29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="M29" t="n">
-        <v>19.9</v>
+        <v>16.9</v>
       </c>
       <c r="N29" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>15.3</v>
+        <v>18.6</v>
       </c>
       <c r="F30" t="n">
-        <v>58.2</v>
+        <v>96.8</v>
       </c>
       <c r="G30" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K30" s="6" t="n">
         <v>0.52</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>0.53</v>
       </c>
       <c r="L30" t="n">
         <v>4.3</v>
       </c>
       <c r="M30" t="n">
-        <v>16.7</v>
+        <v>19.8</v>
       </c>
       <c r="N30" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="31">
@@ -9211,7 +9467,7 @@
         <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
         <v>0.04</v>
@@ -9249,284 +9505,284 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="F32" t="n">
-        <v>59.4</v>
+        <v>59.9</v>
       </c>
       <c r="G32" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H32" t="n">
         <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="J32" t="n">
         <v>0.24</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L32" t="n">
         <v>3.7</v>
       </c>
       <c r="M32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N32" t="n">
         <v>16.1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>15.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E33" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>61.9</v>
+        <v>79.3</v>
       </c>
       <c r="G33" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="I33" t="n">
-        <v>9.300000000000001</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="L33" t="n">
         <v>3.6</v>
       </c>
       <c r="M33" t="n">
-        <v>11.9</v>
+        <v>17</v>
       </c>
       <c r="N33" t="n">
-        <v>11.7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>19.3</v>
+        <v>13.4</v>
       </c>
       <c r="F34" t="n">
-        <v>87.3</v>
+        <v>74.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="H34" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>17.7</v>
+        <v>35.7</v>
       </c>
       <c r="J34" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="L34" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="M34" t="n">
-        <v>16.4</v>
+        <v>18.4</v>
       </c>
       <c r="N34" t="n">
-        <v>16.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="F35" t="n">
-        <v>79</v>
+        <v>55.1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>21.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="L35" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="M35" t="n">
-        <v>16.9</v>
+        <v>10.9</v>
       </c>
       <c r="N35" t="n">
-        <v>15.9</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E36" t="n">
-        <v>13.4</v>
+        <v>15.6</v>
       </c>
       <c r="F36" t="n">
-        <v>74.5</v>
+        <v>66.8</v>
       </c>
       <c r="G36" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="I36" t="n">
-        <v>35.7</v>
+        <v>14.4</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0.44</v>
       </c>
       <c r="L36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>18.4</v>
+        <v>13.4</v>
       </c>
       <c r="N36" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>15.6</v>
+        <v>16.2</v>
       </c>
       <c r="F37" t="n">
-        <v>67</v>
+        <v>72.8</v>
       </c>
       <c r="G37" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H37" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I37" t="n">
-        <v>14.5</v>
+        <v>17.1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="L37" t="n">
         <v>3.2</v>
       </c>
       <c r="M37" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="N37" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="38">
@@ -9552,16 +9808,16 @@
         <v>15.5</v>
       </c>
       <c r="F38" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G38" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H38" t="n">
         <v>1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J38" t="n">
         <v>0.05</v>
@@ -9573,10 +9829,10 @@
         <v>3.1</v>
       </c>
       <c r="M38" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="N38" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
@@ -9602,7 +9858,7 @@
         <v>17.8</v>
       </c>
       <c r="F39" t="n">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G39" t="n">
         <v>0.47</v>
@@ -9649,34 +9905,34 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="F40" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="G40" t="n">
         <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="L40" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="N40" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="41"/>
@@ -9778,107 +10034,107 @@
         <v>67.09999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0.47</v>
       </c>
       <c r="J44" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K44" t="n">
+        <v>17</v>
+      </c>
+      <c r="L44" t="n">
         <v>16.9</v>
-      </c>
-      <c r="L44" t="n">
-        <v>16.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="E45" t="n">
-        <v>11.1</v>
+        <v>8.5</v>
       </c>
       <c r="F45" t="n">
-        <v>6.9</v>
+        <v>4.9</v>
       </c>
       <c r="G45" t="n">
-        <v>94.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="J45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K45" t="n">
-        <v>19.8</v>
+        <v>16.1</v>
       </c>
       <c r="L45" t="n">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="F46" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="G46" t="n">
-        <v>75.2</v>
+        <v>95.8</v>
       </c>
       <c r="H46" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="J46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K46" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L46" t="n">
-        <v>15.3</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="47">
@@ -9901,16 +10157,16 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="F47" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="G47" t="n">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0.4</v>
@@ -9945,19 +10201,19 @@
         <v>0.96</v>
       </c>
       <c r="E48" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F48" t="n">
         <v>5.1</v>
       </c>
       <c r="G48" t="n">
-        <v>89.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="H48" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J48" t="n">
         <v>2.9</v>
@@ -9972,33 +10228,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="F49" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="G49" t="n">
-        <v>76.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="H49" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0.36</v>
@@ -10007,42 +10263,42 @@
         <v>2.6</v>
       </c>
       <c r="K49" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="L49" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="G50" t="n">
-        <v>82.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0.35</v>
@@ -10051,10 +10307,10 @@
         <v>2.5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="L50" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="51">
@@ -10083,13 +10339,13 @@
         <v>4.8</v>
       </c>
       <c r="G51" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H51" t="n">
         <v>0.37</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="J51" t="n">
         <v>2.4</v>
@@ -10098,7 +10354,7 @@
         <v>14.2</v>
       </c>
       <c r="L51" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="52">
@@ -10121,16 +10377,16 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="F52" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="G52" t="n">
-        <v>77.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0.32</v>
@@ -10139,10 +10395,10 @@
         <v>2.3</v>
       </c>
       <c r="K52" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="L52" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="53">
@@ -10236,89 +10492,89 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="F55" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G55" t="n">
-        <v>60</v>
+        <v>50.7</v>
       </c>
       <c r="H55" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>2.1</v>
       </c>
       <c r="K55" t="n">
-        <v>12.8</v>
+        <v>11.5</v>
       </c>
       <c r="L55" t="n">
-        <v>12.1</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E56" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="F56" t="n">
         <v>4.3</v>
       </c>
       <c r="G56" t="n">
-        <v>50.7</v>
+        <v>58.3</v>
       </c>
       <c r="H56" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="J56" t="n">
         <v>2.1</v>
       </c>
       <c r="K56" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="L56" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="57">
@@ -10341,104 +10597,104 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="F57" t="n">
         <v>3</v>
       </c>
       <c r="G57" t="n">
-        <v>40.6</v>
+        <v>39.7</v>
       </c>
       <c r="H57" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J57" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L57" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F58" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="G58" t="n">
-        <v>75.3</v>
+        <v>57</v>
       </c>
       <c r="H58" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="J58" t="n">
         <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>14.8</v>
+        <v>12.1</v>
       </c>
       <c r="L58" t="n">
-        <v>14.8</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="F59" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="G59" t="n">
-        <v>56.6</v>
+        <v>76</v>
       </c>
       <c r="H59" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>0.28</v>
@@ -10447,10 +10703,10 @@
         <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="60">
@@ -10479,7 +10735,7 @@
         <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>58.3</v>
+        <v>58.5</v>
       </c>
       <c r="H60" t="n">
         <v>0.32</v>
@@ -10517,28 +10773,28 @@
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F61" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G61" t="n">
-        <v>66.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H61" t="n">
         <v>0.32</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J61" t="n">
         <v>1.9</v>
       </c>
       <c r="K61" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="L61" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="62">
@@ -10561,13 +10817,13 @@
         <v>0.95</v>
       </c>
       <c r="E62" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="F62" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="G62" t="n">
-        <v>53.4</v>
+        <v>51.9</v>
       </c>
       <c r="H62" t="n">
         <v>0.33</v>
@@ -10579,171 +10835,171 @@
         <v>1.9</v>
       </c>
       <c r="K62" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="L62" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="E63" t="n">
-        <v>10.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="G63" t="n">
-        <v>93.3</v>
+        <v>71.5</v>
       </c>
       <c r="H63" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="J63" t="n">
         <v>1.8</v>
       </c>
       <c r="K63" t="n">
-        <v>20.3</v>
+        <v>14.4</v>
       </c>
       <c r="L63" t="n">
-        <v>10.1</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="E64" t="n">
-        <v>8.9</v>
+        <v>10.7</v>
       </c>
       <c r="F64" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="G64" t="n">
-        <v>71.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="J64" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K64" t="n">
-        <v>14.4</v>
+        <v>19.9</v>
       </c>
       <c r="L64" t="n">
-        <v>13.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="G65" t="n">
-        <v>66.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="H65" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="J65" t="n">
         <v>1.7</v>
       </c>
       <c r="K65" t="n">
-        <v>13.4</v>
+        <v>9.6</v>
       </c>
       <c r="L65" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="F66" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>45.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H66" t="n">
         <v>0.28</v>
@@ -10755,39 +11011,39 @@
         <v>1.7</v>
       </c>
       <c r="K66" t="n">
-        <v>9.699999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="L66" t="n">
-        <v>9.699999999999999</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Michael Wilson</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="F67" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G67" t="n">
-        <v>48.9</v>
+        <v>42.7</v>
       </c>
       <c r="H67" t="n">
         <v>0.27</v>
@@ -10799,10 +11055,10 @@
         <v>1.6</v>
       </c>
       <c r="K67" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="L67" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="68"/>
@@ -10942,13 +11198,13 @@
         <v>8.1</v>
       </c>
       <c r="F72" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G72" t="n">
         <v>57.3</v>
       </c>
       <c r="H72" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="I72" s="6" t="n">
         <v>0.38</v>
@@ -10957,10 +11213,10 @@
         <v>2.8</v>
       </c>
       <c r="K72" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="L72" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="73">
@@ -10989,7 +11245,7 @@
         <v>4.9</v>
       </c>
       <c r="G73" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="H73" t="n">
         <v>0.43</v>
@@ -11027,16 +11283,16 @@
         <v>0.95</v>
       </c>
       <c r="E74" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="F74" t="n">
         <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>66.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H74" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I74" s="6" t="n">
         <v>0.37</v>
@@ -11045,98 +11301,98 @@
         <v>2.6</v>
       </c>
       <c r="K74" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="L74" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Colby Parkinson</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="F75" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="G75" t="n">
-        <v>42.4</v>
+        <v>66.5</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J75" t="n">
         <v>2.3</v>
       </c>
       <c r="K75" t="n">
-        <v>10.7</v>
+        <v>16.6</v>
       </c>
       <c r="L75" t="n">
-        <v>10.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Colby Parkinson</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E76" t="n">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="F76" t="n">
-        <v>7.7</v>
+        <v>4.1</v>
       </c>
       <c r="G76" t="n">
-        <v>66.09999999999999</v>
+        <v>42.3</v>
       </c>
       <c r="H76" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J76" t="n">
         <v>2.3</v>
       </c>
       <c r="K76" t="n">
-        <v>16.5</v>
+        <v>10.7</v>
       </c>
       <c r="L76" t="n">
-        <v>16.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="77">
@@ -11165,10 +11421,10 @@
         <v>4.7</v>
       </c>
       <c r="G77" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="H77" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0.29</v>
@@ -11180,127 +11436,127 @@
         <v>12</v>
       </c>
       <c r="L77" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kyle Pitts</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D78" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E78" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F78" t="n">
-        <v>3.4</v>
+        <v>5.3</v>
       </c>
       <c r="G78" t="n">
-        <v>33.1</v>
+        <v>55</v>
       </c>
       <c r="H78" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="J78" t="n">
         <v>2</v>
       </c>
       <c r="K78" t="n">
-        <v>8.6</v>
+        <v>12.9</v>
       </c>
       <c r="L78" t="n">
-        <v>8.6</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Kyle Pitts</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="D79" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>8.9</v>
+        <v>5</v>
       </c>
       <c r="F79" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="G79" t="n">
-        <v>62</v>
+        <v>32.8</v>
       </c>
       <c r="H79" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="J79" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>13.8</v>
+        <v>8.6</v>
       </c>
       <c r="L79" t="n">
-        <v>13.7</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D80" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>5.7</v>
       </c>
       <c r="G80" t="n">
-        <v>42.9</v>
+        <v>62.1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I80" s="6" t="n">
         <v>0.27</v>
@@ -11309,54 +11565,54 @@
         <v>1.9</v>
       </c>
       <c r="K80" t="n">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="L80" t="n">
-        <v>10.2</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Pat Freiermuth</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="F81" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G81" t="n">
-        <v>34.9</v>
+        <v>42.9</v>
       </c>
       <c r="H81" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J81" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K81" t="n">
-        <v>8.9</v>
+        <v>10.3</v>
       </c>
       <c r="L81" t="n">
-        <v>8.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="82">
@@ -11429,10 +11685,10 @@
         <v>4</v>
       </c>
       <c r="G83" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I83" s="6" t="n">
         <v>0.27</v>
@@ -11470,10 +11726,10 @@
         <v>4.8</v>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G84" t="n">
-        <v>28.7</v>
+        <v>29.5</v>
       </c>
       <c r="H84" t="n">
         <v>0.27</v>
@@ -11485,17 +11741,17 @@
         <v>1.7</v>
       </c>
       <c r="K84" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="L84" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="85"/>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.2; SF 7.9; HOU 7.8; LA 7.8; GB 7.7; CIN 7.6; MIN 7.5; ATL 7.5; DAL 7.5; DEN 7.5</t>
+          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.3; SF 7.9; HOU 7.9; GB 7.8; LA 7.8; CIN 7.6; DAL 7.5; MIN 7.5; DEN 7.5; ATL 7.5</t>
         </is>
       </c>
     </row>
@@ -11614,16 +11870,16 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.773</v>
+        <v>0.779</v>
       </c>
       <c r="G5" t="n">
-        <v>-341</v>
+        <v>-353</v>
       </c>
       <c r="H5" t="n">
-        <v>-223</v>
+        <v>-229</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>1</v>
@@ -11690,16 +11946,16 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.652</v>
       </c>
       <c r="G7" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="H7" t="n">
-        <v>-138</v>
+        <v>-139</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
@@ -11728,16 +11984,16 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.647</v>
+        <v>0.6459999999999999</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.647</v>
+        <v>0.6459999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-183</v>
       </c>
       <c r="H8" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>1</v>
@@ -11766,16 +12022,16 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.6</v>
+        <v>0.601</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.6</v>
+        <v>0.601</v>
       </c>
       <c r="G9" t="n">
-        <v>-150</v>
+        <v>-151</v>
       </c>
       <c r="H9" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
@@ -11808,16 +12064,16 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0.579</v>
+        <v>0.586</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.579</v>
+        <v>0.586</v>
       </c>
       <c r="G10" t="n">
-        <v>-138</v>
+        <v>-142</v>
       </c>
       <c r="H10" t="n">
-        <v>-107</v>
+        <v>-110</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>1</v>
@@ -11888,16 +12144,16 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="G12" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="H12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>1</v>
@@ -11930,16 +12186,16 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.525</v>
+        <v>0.52</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.525</v>
+        <v>0.52</v>
       </c>
       <c r="G13" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H13" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>1</v>
@@ -11968,16 +12224,16 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.508</v>
+        <v>0.507</v>
       </c>
       <c r="G14" t="n">
         <v>-103</v>
       </c>
       <c r="H14" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1</v>
@@ -11991,35 +12247,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.47</v>
+        <v>0.476</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.47</v>
+        <v>0.476</v>
       </c>
       <c r="G15" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>1</v>
@@ -12029,35 +12285,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.467</v>
+        <v>0.474</v>
       </c>
       <c r="G16" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H16" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1</v>
@@ -12067,17 +12323,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12086,74 +12342,78 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.46</v>
+        <v>0.475</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.46</v>
+        <v>0.452</v>
       </c>
       <c r="G17" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.459</v>
+        <v>0.466</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.459</v>
+        <v>0.446</v>
       </c>
       <c r="G18" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H18" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Bucky Irving</t>
+          <t>Jaylen Warren</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12162,58 +12422,54 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.468</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.445</v>
+        <v>0.4379999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="H19" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H20" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>1</v>
@@ -12223,35 +12479,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>J.K. Dobbins</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.4320000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H21" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
@@ -12261,55 +12517,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.45</v>
+        <v>0.417</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.431</v>
+        <v>0.417</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="H22" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -12318,40 +12574,36 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.435</v>
+        <v>0.415</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="G23" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="H23" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>opp QB: QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12360,21 +12612,25 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.412</v>
+        <v>0.436</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.412</v>
+        <v>0.415</v>
       </c>
       <c r="G24" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H24" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>opp QB: QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12398,16 +12654,16 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="G25" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H25" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
@@ -12478,16 +12734,16 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.402</v>
+        <v>0.407</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.385</v>
+        <v>0.389</v>
       </c>
       <c r="G27" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H27" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0.96</v>
@@ -12497,82 +12753,82 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.38</v>
+        <v>0.382</v>
       </c>
       <c r="G28" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H28" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.376</v>
+        <v>0.371</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.376</v>
+        <v>0.371</v>
       </c>
       <c r="G29" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H29" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12596,16 +12852,16 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="G30" t="n">
         <v>172</v>
       </c>
       <c r="H30" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>1</v>
@@ -12634,16 +12890,16 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="G31" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H31" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>1</v>
@@ -12653,17 +12909,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12672,101 +12928,105 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="G32" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H32" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>opp QB: QB1 designation (start probability 65%)</t>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MarShawn Lloyd</t>
+          <t>Brock Bowers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.356</v>
+        <v>0.373</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="G33" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H33" t="n">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brock Bowers</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.374</v>
+        <v>0.351</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.355</v>
+        <v>0.351</v>
       </c>
       <c r="G34" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H34" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>opp QB: QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="35"/>
     <row r="36">
@@ -12820,10 +13080,10 @@
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>0.415</v>
+        <v>0.422</v>
       </c>
       <c r="E38" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
@@ -12866,10 +13126,10 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.263</v>
+        <v>0.264</v>
       </c>
       <c r="E40" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="41">
@@ -12889,10 +13149,10 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.253</v>
+        <v>0.257</v>
       </c>
       <c r="E41" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42">
@@ -12935,10 +13195,10 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.195</v>
+        <v>0.205</v>
       </c>
       <c r="E43" t="n">
-        <v>413</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44">
@@ -12967,47 +13227,47 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.164</v>
+        <v>0.162</v>
       </c>
       <c r="E45" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.157</v>
+        <v>0.159</v>
       </c>
       <c r="E46" t="n">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="47">
@@ -13027,10 +13287,10 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>0.147</v>
+        <v>0.148</v>
       </c>
       <c r="E47" t="n">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="48"/>
@@ -13085,10 +13345,10 @@
         </is>
       </c>
       <c r="D51" s="6" t="n">
-        <v>0.22</v>
+        <v>0.218</v>
       </c>
       <c r="E51" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="52">
@@ -13108,10 +13368,10 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.193</v>
+        <v>0.197</v>
       </c>
       <c r="E52" t="n">
-        <v>419</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53">
@@ -13131,10 +13391,10 @@
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>0.181</v>
+        <v>0.182</v>
       </c>
       <c r="E53" t="n">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="54">
@@ -13154,10 +13414,10 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="E54" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="55">
@@ -13203,7 +13463,7 @@
         <v>0.167</v>
       </c>
       <c r="E56" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57">
@@ -13223,72 +13483,72 @@
         </is>
       </c>
       <c r="D57" s="6" t="n">
-        <v>0.161</v>
+        <v>0.16</v>
       </c>
       <c r="E57" t="n">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>0.157</v>
+        <v>0.142</v>
       </c>
       <c r="E58" t="n">
-        <v>536</v>
+        <v>603</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.141</v>
+        <v>0.138</v>
       </c>
       <c r="E59" t="n">
-        <v>608</v>
+        <v>624</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Bucky Irving</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
@@ -13302,7 +13562,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Tre Tucker (LV) 25% fair +301, take at +350+; Alvin Kamara (NO) 25% fair +303, take at +351+; George Holani (SEA) 25% fair +308, take at +357+; Samaje Perine (CIN) 24% fair +314, take at +363+; Travis Kelce (KC) 25% fair +303, take at +351+; Michael Wilson (ARI) 24% fair +323, take at +373+; Darius Cooper (PHI) 24% fair +325, take at +376+; Mike Gesicki (CIN) 23% fair +328, take at +380+; Darnell Washington (PIT) 23% fair +330, take at +382+; Wan'Dale Robinson (TEN) 23% fair +331, take at +383+; KC Concepcion (CLE) 24% fair +313, take at +362+; Jahan Dotson (ATL) 23% fair +342, take at +395+; Xavier Worthy (KC) 22% fair +346, take at +399+; Ryan Flournoy (DAL) 22% fair +348, take at +402+; Darren Waller (CAR) 23% fair +326, take at +378+; Kaelon Black (SF) 22% fair +354, take at +409+; Bo Nix (DEN) 22% fair +356, take at +410+; Devaughn Vele (NO) 22% fair +358, take at +413+; Malik Washington (MIA) 22% fair +361, take at +417+; Jameson Williams (DET) 22% fair +363, take at +418+</t>
+          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Alvin Kamara (NO) 25% fair +303, take at +351+; George Holani (SEA) 25% fair +306, take at +354+; Malik Nabers (NYG) 25% fair +307, take at +356+; Tre Tucker (LV) 24% fair +309, take at +358+; Samaje Perine (CIN) 24% fair +312, take at +361+; Michael Wilson (ARI) 24% fair +319, take at +370+; Travis Kelce (KC) 25% fair +304, take at +352+; Mike Gesicki (CIN) 24% fair +323, take at +373+; Wan'Dale Robinson (TEN) 24% fair +323, take at +374+; Darnell Washington (PIT) 23% fair +330, take at +382+; Jahan Dotson (ATL) 23% fair +344, take at +398+; Darius Cooper (PHI) 22% fair +347, take at +400+; Ryan Flournoy (DAL) 22% fair +348, take at +401+; Darren Waller (CAR) 24% fair +324, take at +375+; Xavier Worthy (KC) 22% fair +350, take at +403+; Kaelon Black (SF) 22% fair +354, take at +409+; Jameson Williams (DET) 22% fair +358, take at +413+; Devaughn Vele (NO) 22% fair +358, take at +413+; KC Concepcion (CLE) 23% fair +337, take at +389+; Carnell Tate (TEN) 22% fair +362, take at +417+</t>
         </is>
       </c>
     </row>
@@ -13317,7 +13577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13346,7 +13606,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>484 lines screened: 49 PLAY (24 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 47 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
+          <t>484 lines screened: 50 PLAY (27 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 44 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
         </is>
       </c>
     </row>
@@ -13425,39 +13685,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>IND@MIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11.5</v>
+        <v>26.5</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0.83</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-198</v>
+        <v>-200</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13466,53 +13726,49 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-182</v>
+        <v>-200</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -13523,29 +13779,29 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13554,16 +13810,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>16.5</v>
+        <v>2.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I7" t="n">
-        <v>-176</v>
+        <v>-184</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -13578,7 +13834,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
         </is>
       </c>
     </row>
@@ -13590,26 +13846,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.77</v>
@@ -13631,7 +13887,11 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -13641,12 +13901,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -13656,11 +13916,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.77</v>
@@ -13673,7 +13933,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13682,31 +13942,27 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13715,7 +13971,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.77</v>
@@ -13728,7 +13984,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13737,7 +13993,11 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -13747,12 +14007,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Xavier Hutchinson</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13762,11 +14022,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>0.76</v>
@@ -13775,11 +14035,11 @@
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -13788,31 +14048,27 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -13821,7 +14077,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>13.5</v>
+        <v>1.5</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.76</v>
@@ -13834,7 +14090,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -13843,7 +14099,11 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -13878,10 +14138,10 @@
         <v>0.75</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I13" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13899,22 +14159,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>George Holani</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -13923,20 +14183,20 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.75</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I14" t="n">
-        <v>-166</v>
+        <v>-168</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -13945,11 +14205,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -13959,12 +14215,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -13978,20 +14234,20 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.5</v>
+        <v>14.5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-164</v>
+        <v>-168</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14000,11 +14256,7 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14014,17 +14266,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -14033,20 +14285,20 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I16" t="n">
-        <v>-161</v>
+        <v>-167</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14055,45 +14307,49 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tommy Tremble</t>
+          <t>Samaje Perine</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I17" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -14108,51 +14364,51 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IND@MIN</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26.5</v>
+        <v>3.5</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0.73</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I18" t="n">
-        <v>-159</v>
+        <v>-161</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14171,12 +14427,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Tommy Tremble</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14190,20 +14446,20 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H19" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="I19" t="n">
-        <v>-157</v>
+        <v>-160</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14212,27 +14468,31 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -14241,16 +14501,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="I20" t="n">
-        <v>-156</v>
+        <v>-159</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -14273,26 +14533,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>15.5</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0.72</v>
@@ -14301,11 +14561,11 @@
         <v>0.61</v>
       </c>
       <c r="I21" t="n">
-        <v>-155</v>
+        <v>-157</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14324,17 +14584,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -14343,7 +14603,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>84.5</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>0.72</v>
@@ -14352,7 +14612,7 @@
         <v>0.61</v>
       </c>
       <c r="I22" t="n">
-        <v>-155</v>
+        <v>-157</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -14365,53 +14625,49 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="I23" t="n">
-        <v>-153</v>
+        <v>-156</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -14420,49 +14676,53 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I24" t="n">
-        <v>-151</v>
+        <v>-154</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -14471,40 +14731,36 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>0.7</v>
@@ -14517,7 +14773,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -14528,14 +14784,14 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -14545,21 +14801,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>0.7</v>
@@ -14572,7 +14828,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -14641,31 +14897,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14.5</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>0.7</v>
@@ -14674,7 +14930,7 @@
         <v>0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-149</v>
+        <v>-150</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14687,7 +14943,11 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -14697,12 +14957,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -14716,20 +14976,20 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>80.5</v>
+        <v>69.5</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-149</v>
+        <v>-147</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14738,7 +14998,11 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -14748,17 +15012,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Jake Ferguson</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -14767,20 +15031,20 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I30" t="n">
-        <v>-148</v>
+        <v>-146</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -14789,7 +15053,11 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14896,31 +15164,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>0.68</v>
@@ -14929,11 +15197,11 @@
         <v>0.59</v>
       </c>
       <c r="I33" t="n">
-        <v>-143</v>
+        <v>-145</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14942,53 +15210,49 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bijan Robinson</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>18.5</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I34" t="n">
-        <v>-143</v>
+        <v>-141</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14997,7 +15261,11 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15007,12 +15275,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15026,20 +15294,20 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>68.5</v>
+        <v>42.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I35" t="n">
-        <v>-143</v>
+        <v>-140</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15048,11 +15316,7 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15062,17 +15326,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -15081,20 +15345,20 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>42.5</v>
+        <v>3.5</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H36" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="I36" t="n">
-        <v>-140</v>
+        <v>-138</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15108,44 +15372,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H37" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="I37" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15154,11 +15418,7 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15190,13 +15450,13 @@
         <v>8.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="H38" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="I38" t="n">
-        <v>-139</v>
+        <v>-136</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -15214,44 +15474,44 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pass_cmp</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>21.5</v>
+        <v>54.5</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0.65</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I39" t="n">
-        <v>-136</v>
+        <v>-134</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15270,17 +15530,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -15289,20 +15549,20 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>54.5</v>
+        <v>7.5</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="I40" t="n">
-        <v>-134</v>
+        <v>-133</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15311,7 +15571,11 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15321,17 +15585,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AJ Dillon</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -15340,7 +15604,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.5</v>
+        <v>80.5</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0.64</v>
@@ -15353,7 +15617,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15362,16 +15626,12 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -15381,12 +15641,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -15395,7 +15655,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6.5</v>
+        <v>64.5</v>
       </c>
       <c r="G42" s="6" t="n">
         <v>0.64</v>
@@ -15408,7 +15668,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15422,31 +15682,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MIA@NYJ</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>AJ Dillon</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>64.5</v>
+        <v>3.5</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0.64</v>
@@ -15455,11 +15715,11 @@
         <v>0.57</v>
       </c>
       <c r="I43" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -15468,7 +15728,11 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15506,7 +15770,7 @@
         <v>0.57</v>
       </c>
       <c r="I44" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -15528,22 +15792,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -15552,7 +15816,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>80.5</v>
+        <v>6.5</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0.64</v>
@@ -15561,11 +15825,11 @@
         <v>0.57</v>
       </c>
       <c r="I45" t="n">
-        <v>-132</v>
+        <v>-131</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -15584,12 +15848,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -15603,7 +15867,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="G46" s="6" t="n">
         <v>0.63</v>
@@ -15612,11 +15876,11 @@
         <v>0.57</v>
       </c>
       <c r="I46" t="n">
-        <v>-131</v>
+        <v>-130</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -15635,39 +15899,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="G47" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-131</v>
+        <v>-130</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -15686,12 +15950,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -15705,20 +15969,20 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14.5</v>
+        <v>6.5</v>
       </c>
       <c r="G48" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>-131</v>
+        <v>-129</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -15732,7 +15996,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -15742,21 +16006,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>RJ Harvey</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0.63</v>
@@ -15765,11 +16029,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>-130</v>
+        <v>-129</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -15783,22 +16047,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Dohnte Meyers</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pass_yds</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -15807,7 +16071,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>227.5</v>
+        <v>13.5</v>
       </c>
       <c r="G50" s="6" t="n">
         <v>0.62</v>
@@ -15816,11 +16080,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-126</v>
+        <v>-128</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -15829,7 +16093,11 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -15867,7 +16135,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -15890,12 +16158,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dohnte Meyers</t>
+          <t>Austin Hooper</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -15909,7 +16177,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0.61</v>
@@ -15922,7 +16190,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -15931,11 +16199,7 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -15945,26 +16209,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.5</v>
+        <v>21.5</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0.61</v>
@@ -15973,11 +16237,11 @@
         <v>0.55</v>
       </c>
       <c r="I53" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -15986,31 +16250,27 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LEAN</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>IND@MIN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -16019,20 +16279,20 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>29.5</v>
+        <v>1.5</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="I54" t="n">
-        <v>-203</v>
+        <v>-125</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -16040,11 +16300,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>model vs own record</t>
-        </is>
-      </c>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -16055,17 +16311,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -16074,20 +16330,20 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5.5</v>
+        <v>29.5</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="I55" t="n">
-        <v>-173</v>
+        <v>-207</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -16095,12 +16351,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>model vs own record</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16110,39 +16366,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pierre Strong</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-171</v>
+        <v>-174</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1/2</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -16151,7 +16407,11 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16238,13 +16498,13 @@
         <v>65.5</v>
       </c>
       <c r="G58" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H58" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="I58" t="n">
-        <v>-156</v>
+        <v>-154</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -16275,17 +16535,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IND@MIN</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -16294,20 +16554,20 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="G59" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I59" t="n">
-        <v>-156</v>
+        <v>-153</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16315,12 +16575,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -16330,17 +16590,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -16349,7 +16609,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="G60" s="6" t="n">
         <v>0.71</v>
@@ -16358,11 +16618,11 @@
         <v>0.6</v>
       </c>
       <c r="I60" t="n">
-        <v>-153</v>
+        <v>-152</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16371,11 +16631,7 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -16385,12 +16641,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -16404,20 +16660,20 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="G61" s="6" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I61" t="n">
-        <v>-152</v>
+        <v>-146</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -16426,7 +16682,11 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -16436,39 +16696,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>17.5</v>
+        <v>41.5</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="I62" t="n">
-        <v>-147</v>
+        <v>-145</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -16476,10 +16736,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
@@ -16491,12 +16755,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -16506,20 +16770,20 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>41.5</v>
+        <v>46.5</v>
       </c>
       <c r="G63" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H63" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="I63" t="n">
-        <v>-146</v>
+        <v>-142</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -16536,11 +16800,7 @@
           <t>same bet as sibling line</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16575,10 +16835,10 @@
         <v>0.67</v>
       </c>
       <c r="H64" s="6" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I64" t="n">
-        <v>-140</v>
+        <v>-141</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -16605,12 +16865,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -16620,11 +16880,11 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>46.5</v>
+        <v>63.5</v>
       </c>
       <c r="G65" s="6" t="n">
         <v>0.65</v>
@@ -16637,7 +16897,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -16645,12 +16905,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16660,12 +16920,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -16675,11 +16935,11 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>63.5</v>
+        <v>19.5</v>
       </c>
       <c r="G66" s="6" t="n">
         <v>0.65</v>
@@ -16688,11 +16948,11 @@
         <v>0.58</v>
       </c>
       <c r="I66" t="n">
-        <v>-136</v>
+        <v>-135</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -16701,11 +16961,7 @@
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -16715,17 +16971,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -16734,20 +16990,20 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>19.5</v>
+        <v>3.5</v>
       </c>
       <c r="G67" s="6" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="H67" s="6" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I67" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -16776,7 +17032,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -16785,16 +17041,16 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="G68" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="I68" t="n">
-        <v>-133</v>
+        <v>-131</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -16822,12 +17078,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -16836,7 +17092,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>14.5</v>
+        <v>27.5</v>
       </c>
       <c r="G69" s="6" t="n">
         <v>0.62</v>
@@ -16849,7 +17105,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0/4</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -16873,12 +17129,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>pass_att</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -16887,7 +17143,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>27.5</v>
+        <v>20.5</v>
       </c>
       <c r="G70" s="6" t="n">
         <v>0.62</v>
@@ -16896,11 +17152,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-127</v>
+        <v>-128</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -16941,7 +17197,7 @@
         <v>65.5</v>
       </c>
       <c r="G71" s="6" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="H71" s="6" t="n">
         <v>0.5600000000000001</v>
@@ -16974,12 +17230,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jahmyr Gibbs</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -16993,7 +17249,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>97.5</v>
+        <v>7.5</v>
       </c>
       <c r="G72" s="6" t="n">
         <v>0.61</v>
@@ -17002,11 +17258,11 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>-126</v>
+        <v>-125</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>0/2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -17015,7 +17271,11 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17025,17 +17285,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>J.K. Dobbins</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -17044,29 +17304,33 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>49.5</v>
+        <v>28.5</v>
       </c>
       <c r="G73" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="H73" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I73" t="n">
         <v>-125</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17076,12 +17340,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Jahmyr Gibbs</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -17095,16 +17359,16 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>13.5</v>
+        <v>97.5</v>
       </c>
       <c r="G74" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="H74" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>-124</v>
+        <v>-125</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -17127,17 +17391,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>pass_att</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -17146,7 +17410,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>28.5</v>
+        <v>23.5</v>
       </c>
       <c r="G75" s="6" t="n">
         <v>0.61</v>
@@ -17155,22 +17419,22 @@
         <v>0.55</v>
       </c>
       <c r="I75" t="n">
-        <v>-124</v>
+        <v>-123</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>fill-in QB (QB1 Out)</t>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
@@ -17182,17 +17446,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Kendre Miller</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -17201,20 +17465,20 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="G76" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="I76" t="n">
-        <v>-124</v>
+        <v>-123</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0/2</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -17223,11 +17487,7 @@
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17237,17 +17497,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>pass_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -17256,7 +17516,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>30.5</v>
+        <v>15.5</v>
       </c>
       <c r="G77" s="6" t="n">
         <v>0.6</v>
@@ -17269,7 +17529,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>0/4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -17288,17 +17548,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kendre Miller</t>
+          <t>Joe Burrow</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -17307,7 +17567,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G78" s="6" t="n">
         <v>0.6</v>
@@ -17320,7 +17580,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -17329,7 +17589,62 @@
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>LEAN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CLE@TEN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cam Ward</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>pass_att</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>OVER</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-122</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/weekly/SLATE_FULL_2026_W07.xlsx
+++ b/docs/weekly/SLATE_FULL_2026_W07.xlsx
@@ -486,7 +486,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T12:01:29Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T12:01:26+00:00. nflverse depth charts: 2026-10-25T06:01:49Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T12:10Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git c21ee9a.</t>
+          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T12:01:29Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T12:01:26+00:00. nflverse depth charts: 2026-10-25T06:01:49Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T12:10Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git 1cd37ed.</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -700,58 +700,58 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks anytime TD + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + GB@DET: Jordan Love pass TD 2+</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.3720000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.51</v>
+        <v>0.507</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E15" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks anytime TD + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 2+</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.509</v>
+        <v>0.507</v>
       </c>
       <c r="D16" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E16" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>SF@ATL: George Kittle anytime TD + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.371</v>
+        <v>0.36</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.507</v>
+        <v>0.478</v>
       </c>
       <c r="D17" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E17" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18"/>
@@ -948,39 +948,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>0.266</v>
+        <v>0.259</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0.433</v>
+        <v>0.416</v>
       </c>
       <c r="D31" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E31" t="n">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>NYG@HOU: Xavier Hutchinson rec O1.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>0.261</v>
+        <v>0.258</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0.421</v>
+        <v>0.414</v>
       </c>
       <c r="D32" t="n">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E32" t="n">
-        <v>329</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33"/>
@@ -1028,77 +1028,77 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.197</v>
+        <v>0.192</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.479</v>
+        <v>0.459</v>
       </c>
       <c r="D37" t="n">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="E37" t="n">
-        <v>469</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.196</v>
+        <v>0.191</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.478</v>
+        <v>0.458</v>
       </c>
       <c r="D38" t="n">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="E38" t="n">
-        <v>470</v>
+        <v>485</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.196</v>
+        <v>0.191</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.476</v>
+        <v>0.457</v>
       </c>
       <c r="D39" t="n">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="E39" t="n">
-        <v>471</v>
+        <v>486</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>0.195</v>
+        <v>0.191</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.472</v>
+        <v>0.457</v>
       </c>
       <c r="D40" t="n">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="E40" t="n">
-        <v>474</v>
+        <v>486</v>
       </c>
     </row>
     <row r="41"/>
@@ -1158,58 +1158,58 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.361</v>
+        <v>0.346</v>
       </c>
       <c r="D45" t="n">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="E45" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Woody Marks rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>0.177</v>
+        <v>0.173</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>0.361</v>
+        <v>0.346</v>
       </c>
       <c r="D46" t="n">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="E46" t="n">
-        <v>533</v>
+        <v>549</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + DAL@PHI: Javonte Williams rush_att U16.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U26.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.174</v>
+        <v>0.172</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0.351</v>
+        <v>0.344</v>
       </c>
       <c r="D47" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="E47" t="n">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="48"/>
@@ -2069,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -2121,33 +2121,40 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>4. Availability prior. Healthy players with no designation carry p_active of about 0.95 (fitted prior), so A.J. Brown's anytime TD is 5% below his conditional number. Inactives (about 90 minutes before each kickoff) replace the prior with certainty.</t>
+          <t>3c. Log hit rates drop zero-usage games (a game with no target or carry is missing from the 'log' column), which flatters OVERs on low-volume players; red-team corrected Hooper, Dillon and Dulcich by hand. No model-versus-market gap flags: there are no prices, so no no-vig anchor exists to measure a gap against.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>5. Anytime-TD board: the 0.10 to 0.20 bin was over-predicted 2.4x in Week 6 in the sim board (frozen-run board: predicted 15.0% vs 9.1% actual, n=55) and the top ten hit 70% against 64% predicted; the W9 postmortem checks the floor. Probabilities are conditional on playing, so discount by the p_active column.</t>
+          <t>4. Availability prior. Healthy players with no designation carry p_active of about 0.95 (fitted prior), so A.J. Brown's anytime TD is 5% below his conditional number. Inactives (about 90 minutes before each kickoff) replace the prior with certainty.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>6. Minor: about two dozen practice-squad or inactive players carry small volumes at 100% active (e.g. players listed IR/PUP who appear in the unmatched-names report).</t>
+          <t>5. Anytime-TD board: the 0.10 to 0.20 bin was over-predicted 2.4x in Week 6 in the sim board (frozen-run board: predicted 15.0% vs 9.1% actual, n=55) and the top ten hit 70% against 64% predicted; the W9 postmortem checks the floor. Probabilities are conditional on playing, so discount by the p_active column.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>7. Nothing here is priced: no book prices and no touchdown prices. A PLAY is a lean at an assumed -110, not an edge. Send a screenshot of any board and I will re-price against the real numbers.</t>
+          <t>6. Minor: about two dozen practice-squad or inactive players carry small volumes at 100% active (e.g. players listed IR/PUP who appear in the unmatched-names report).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>7. Nothing here is priced: no book prices and no touchdown prices. A PLAY is a lean at an assumed -110, not an edge. Send a screenshot of any board and I will re-price against the real numbers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Method: apex-weekly run both tracks, espn_inactives.py, espn_props.py, slate_full.py sim/render, team_tables.py (box score, play-by-play and PFR advanced), league_spm.py.</t>
         </is>
@@ -13577,7 +13584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -13606,7 +13613,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>484 lines screened: 50 PLAY (27 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 44 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
+          <t>484 lines screened: 23 PLAY (14 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 78 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
         </is>
       </c>
     </row>
@@ -13786,22 +13793,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -13810,20 +13817,20 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="I7" t="n">
-        <v>-184</v>
+        <v>-172</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -13834,29 +13841,29 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -13865,20 +13872,20 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16.5</v>
+        <v>2.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="I8" t="n">
-        <v>-175</v>
+        <v>-171</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -13887,31 +13894,27 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -13920,20 +13923,20 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I9" t="n">
-        <v>-173</v>
+        <v>-170</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13942,7 +13945,11 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -13952,12 +13959,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jordan Love</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -13971,20 +13978,20 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I10" t="n">
-        <v>-172</v>
+        <v>-168</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13993,11 +14000,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14007,39 +14010,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I11" t="n">
-        <v>-171</v>
+        <v>-167</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -14048,7 +14051,11 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14058,12 +14065,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Xavier Hutchinson</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -14077,20 +14084,20 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I12" t="n">
-        <v>-170</v>
+        <v>-161</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14099,11 +14106,7 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14113,17 +14116,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Kyren Williams</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -14132,20 +14135,20 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I13" t="n">
-        <v>-168</v>
+        <v>-157</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14159,44 +14162,44 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>13.5</v>
+        <v>84.5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I14" t="n">
-        <v>-168</v>
+        <v>-157</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14210,22 +14213,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -14234,20 +14237,20 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I15" t="n">
-        <v>-168</v>
+        <v>-156</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14256,7 +14259,11 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14266,17 +14273,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Noah Gray</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -14285,20 +14292,20 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-167</v>
+        <v>-150</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14307,31 +14314,27 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -14340,20 +14343,20 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I17" t="n">
-        <v>-162</v>
+        <v>-150</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14364,29 +14367,29 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14395,20 +14398,20 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>17.5</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="I18" t="n">
-        <v>-161</v>
+        <v>-145</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14427,12 +14430,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tommy Tremble</t>
+          <t>Marvin Harrison Jr.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -14442,24 +14445,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I19" t="n">
-        <v>-160</v>
+        <v>-141</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14470,7 +14473,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
         </is>
       </c>
     </row>
@@ -14482,12 +14485,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -14501,20 +14504,20 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-159</v>
+        <v>-138</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14533,39 +14536,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>PIT@NO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15.5</v>
+        <v>21.5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="I21" t="n">
-        <v>-157</v>
+        <v>-136</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14589,7 +14592,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Jameson Williams</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -14603,16 +14606,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>84.5</v>
+        <v>54.5</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.72</v>
+        <v>0.65</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="I22" t="n">
-        <v>-157</v>
+        <v>-134</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -14630,40 +14633,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>7.5</v>
+        <v>80.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.72</v>
+        <v>0.64</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="I23" t="n">
-        <v>-156</v>
+        <v>-132</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -14676,31 +14679,27 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>John Metchie III</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -14709,20 +14708,20 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="I24" t="n">
-        <v>-154</v>
+        <v>-131</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -14731,27 +14730,31 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -14760,20 +14763,20 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="I25" t="n">
-        <v>-151</v>
+        <v>-131</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -14782,31 +14785,27 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -14815,20 +14814,20 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-151</v>
+        <v>-130</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -14837,11 +14836,7 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -14851,12 +14846,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>IND@MIN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Noah Gray</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -14866,24 +14861,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1.5</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="I27" t="n">
-        <v>-150</v>
+        <v>-125</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -14897,22 +14892,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -14921,20 +14916,20 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>70.5</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="I28" t="n">
-        <v>-150</v>
+        <v>-244</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -14942,32 +14937,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14976,20 +14975,20 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>69.5</v>
+        <v>29.5</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="I29" t="n">
-        <v>-147</v>
+        <v>-207</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14997,17 +14996,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -15017,34 +15016,34 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jake Ferguson</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="I30" t="n">
-        <v>-146</v>
+        <v>-175</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15052,7 +15051,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
@@ -15062,44 +15065,44 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17.5</v>
+        <v>5.5</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.59</v>
+        <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-145</v>
+        <v>-174</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15108,22 +15111,26 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15137,20 +15144,20 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I32" t="n">
-        <v>-145</v>
+        <v>-173</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15158,13 +15165,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -15174,7 +15185,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15188,20 +15199,20 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="I33" t="n">
-        <v>-145</v>
+        <v>-168</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15209,50 +15220,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.5</v>
+        <v>197.5</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="I34" t="n">
-        <v>-141</v>
+        <v>-160</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15263,29 +15278,29 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+          <t>fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -15294,20 +15309,20 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>42.5</v>
+        <v>31.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="I35" t="n">
-        <v>-140</v>
+        <v>-156</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15315,28 +15330,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -15345,20 +15364,20 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>65.5</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="I36" t="n">
-        <v>-138</v>
+        <v>-154</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15366,28 +15385,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pass_cmp</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -15396,20 +15423,20 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21.5</v>
+        <v>8.5</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="I37" t="n">
-        <v>-136</v>
+        <v>-154</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15417,28 +15444,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Blake Corum</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -15447,20 +15478,20 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="I38" t="n">
-        <v>-136</v>
+        <v>-153</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15468,28 +15499,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -15498,20 +15537,20 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>54.5</v>
+        <v>4.5</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="I39" t="n">
-        <v>-134</v>
+        <v>-152</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15519,50 +15558,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-133</v>
+        <v>-151</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15570,54 +15613,58 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>80.5</v>
+        <v>17.5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I41" t="n">
-        <v>-132</v>
+        <v>-146</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15626,49 +15673,53 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MIA@NYJ</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Sione Vaki</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>64.5</v>
+        <v>8.5</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I42" t="n">
-        <v>-132</v>
+        <v>-145</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15676,28 +15727,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AJ Dillon</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -15706,20 +15761,20 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>19.5</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I43" t="n">
-        <v>-131</v>
+        <v>-145</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -15727,32 +15782,36 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>John Metchie III</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -15761,20 +15820,20 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>10.5</v>
+        <v>41.5</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I44" t="n">
-        <v>-131</v>
+        <v>-145</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -15782,54 +15841,58 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Tony Pollard</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6.5</v>
+        <v>17.5</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I45" t="n">
-        <v>-131</v>
+        <v>-145</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -15837,50 +15900,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>14.5</v>
+        <v>46.5</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I46" t="n">
-        <v>-130</v>
+        <v>-142</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -15888,50 +15955,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="I47" t="n">
-        <v>-130</v>
+        <v>-141</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -15940,49 +16011,53 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MIA@NYJ</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Malik Willis</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6.5</v>
+        <v>192.5</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I48" t="n">
-        <v>-129</v>
+        <v>-140</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -15990,23 +16065,31 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>RJ Harvey</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -16020,20 +16103,20 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>14.5</v>
+        <v>63.5</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I49" t="n">
-        <v>-129</v>
+        <v>-136</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -16042,27 +16125,31 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dohnte Meyers</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -16071,20 +16158,20 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="G50" s="6" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-128</v>
+        <v>-136</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -16092,50 +16179,50 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Elic Ayomanor</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I51" t="n">
-        <v>-125</v>
+        <v>-136</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -16147,13 +16234,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -16163,34 +16254,34 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin Hooper</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.5</v>
+        <v>19.5</v>
       </c>
       <c r="G52" s="6" t="n">
-        <v>0.61</v>
+        <v>0.65</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="I52" t="n">
-        <v>-125</v>
+        <v>-135</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -16198,1453 +16289,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>PLAY (thin)</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>MIA@NYJ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Greg Dulcich</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>rec_yds</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-125</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2/4</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>PLAY (thin)</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>IND@MIN</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Jauan Jennings</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>rec</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-125</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>4/4</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>CLE@TEN</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-207</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>model vs own record</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CIN@BAL</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Tyler Huntley</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-174</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>CIN@BAL</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tyler Huntley</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>pass_yds</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-160</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>1/3</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Javonte Williams</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-154</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H59" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-153</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>SF@ATL</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Brock Purdy</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H60" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-152</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>TB@CAR</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Chuba Hubbard</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G61" s="6" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="H61" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-146</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CIN@BAL</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Chase Brown</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H62" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-145</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>CLE@TEN</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Quinshon Judkins</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="G63" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H63" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I63" t="n">
-        <v>-142</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>3/5</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NYG@HOU</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G64" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H64" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I64" t="n">
-        <v>-141</v>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NYG@HOU</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="G65" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H65" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-136</v>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>SF@ATL</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Brock Purdy</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G66" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H66" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-135</v>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>PIT@NO</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tyler Shough</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G67" s="6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H67" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-133</v>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>PIT@NO</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tyler Shough</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="G68" s="6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H68" s="6" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-131</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>MIA@NYJ</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Malik Willis</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>pass_att</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G69" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H69" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-128</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>1/5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>MIA@NYJ</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>pass_cmp</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G70" s="6" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H70" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-128</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>TB@CAR</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Bucky Irving</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="G71" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H71" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>-126</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>TB@CAR</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Sean Tucker</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H72" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I72" t="n">
-        <v>-125</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>0/2</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>CIN@BAL</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Tyler Huntley</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>pass_att</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G73" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H73" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>-125</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2/3</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>GB@DET</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Jahmyr Gibbs</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I74" t="n">
-        <v>-125</v>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>pass_cmp</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G75" s="6" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="H75" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I75" t="n">
-        <v>-123</v>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>PIT@NO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Kendre Miller</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G76" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-123</v>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>4/5</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MIA@NYJ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Jaylen Wright</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="G77" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I77" t="n">
-        <v>-123</v>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>0/4</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>CIN@BAL</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Joe Burrow</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G78" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H78" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-123</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2/5</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>CLE@TEN</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Cam Ward</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>pass_att</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="G79" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H79" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I79" t="n">
-        <v>-122</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/weekly/SLATE_FULL_2026_W07.xlsx
+++ b/docs/weekly/SLATE_FULL_2026_W07.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -486,7 +486,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T12:01:29Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T12:01:26+00:00. nflverse depth charts: 2026-10-25T06:01:49Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T12:10Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git 1cd37ed.</t>
+          <t>Inputs used (UTC). ESPN game-summary Outs (5 names per team cap, not the official inactives): 2026-10-25T15:44:22Z. Sleeper status overlay (newer Out replaces the NFL row): 2026-10-25T15:44:16+00:00. nflverse depth charts: 2026-10-25T12:30:46Z; nflverse injuries: no timestamp in the feed. Lines: ESPN/DraftKings fetched 2026-10-25T15:44Z (no prices; the per-line last_updated_utc stamps run ahead of the fetch time and their zone is unverified, so no recency claim is made from them). Official inactives: not used (the ESPN feed carries injuries, not the NFL inactive list). Code: git bbc8319.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Started or finished, excluded from picks: NE@CHI, PIT@NO.</t>
         </is>
       </c>
     </row>
@@ -501,11 +508,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
@@ -570,36 +577,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.723</v>
+        <v>0.725</v>
       </c>
       <c r="D7" t="n">
         <v>119</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="D8" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E8" t="n">
         <v>146</v>
@@ -608,39 +615,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.722</v>
+        <v>0.713</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E9" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jared Goff pass TD 1+</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.455</v>
+        <v>0.451</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.721</v>
+        <v>0.71</v>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E10" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11"/>
@@ -685,54 +692,54 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>0.41</v>
+        <v>0.408</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.545</v>
+        <v>0.5379999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E14" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + GB@DET: Jordan Love pass TD 2+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 2+</t>
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.507</v>
+        <v>0.506</v>
       </c>
       <c r="D15" t="n">
         <v>171</v>
       </c>
       <c r="E15" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 2+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U25.5 + GB@DET: Jordan Love pass TD 2+</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>0.369</v>
+        <v>0.364</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.507</v>
+        <v>0.494</v>
       </c>
       <c r="D16" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E16" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17">
@@ -742,13 +749,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>0.36</v>
+        <v>0.359</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.478</v>
+        <v>0.476</v>
       </c>
       <c r="D17" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E17" t="n">
         <v>212</v>
@@ -799,77 +806,77 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>0.304</v>
+        <v>0.3</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.602</v>
+        <v>0.589</v>
       </c>
       <c r="D22" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="E22" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>0.303</v>
+        <v>0.298</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>0.601</v>
+        <v>0.585</v>
       </c>
       <c r="D23" t="n">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E23" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>0.303</v>
+        <v>0.296</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>0.599</v>
+        <v>0.579</v>
       </c>
       <c r="D24" t="n">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="E24" t="n">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + GB@DET: Jared Goff pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + GB@DET: Jared Goff pass TD 1+</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>0.301</v>
+        <v>0.296</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>0.594</v>
+        <v>0.5770000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E25" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26"/>
@@ -910,39 +917,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>0.273</v>
+        <v>0.272</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>0.454</v>
+        <v>0.447</v>
       </c>
       <c r="D29" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E29" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>IND@MIN: Kyler Murray rush_yds U25.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>0.273</v>
+        <v>0.268</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>0.454</v>
+        <v>0.4370000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31">
@@ -955,7 +962,7 @@
         <v>0.259</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="D31" t="n">
         <v>286</v>
@@ -974,7 +981,7 @@
         <v>0.258</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>0.414</v>
+        <v>0.412</v>
       </c>
       <c r="D32" t="n">
         <v>287</v>
@@ -1028,77 +1035,77 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + DEN@ARI: Tyler Allgeier rec U2.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>0.192</v>
+        <v>0.19</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.459</v>
+        <v>0.453</v>
       </c>
       <c r="D37" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E37" t="n">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + GB@DET: Jordan Love pass TD 1+</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>0.458</v>
+        <v>0.451</v>
       </c>
       <c r="D38" t="n">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E38" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + GB@DET: Jordan Love pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + DEN@ARI: Tyler Allgeier rec U2.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.457</v>
+        <v>0.45</v>
       </c>
       <c r="D39" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E39" t="n">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + LA@LV: Matthew Stafford pass TD 1+</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>0.191</v>
+        <v>0.189</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.457</v>
+        <v>0.448</v>
       </c>
       <c r="D40" t="n">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E40" t="n">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="41"/>
@@ -1139,77 +1146,77 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + CIN@BAL: Chase Brown rush_att O11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + IND@MIN: Kyler Murray rush_yds U25.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B44" s="6" t="n">
-        <v>0.182</v>
+        <v>0.178</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.363</v>
       </c>
       <c r="D44" t="n">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="E44" t="n">
-        <v>515</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="D45" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E45" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CIN@BAL: Chase Brown rush_att O11.5 + DEN@ARI: Tyler Allgeier rec U2.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B46" s="6" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="D46" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E46" t="n">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IND@MIN: Kyler Murray rush_yds U26.5 + NYG@HOU: Xavier Hutchinson rec O1.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
+          <t>CIN@BAL: Chase Brown rush_att O11.5 + TB@CAR: Bryce Young rush_yds U11.5 + SF@ATL: George Kittle anytime TD + SF@ATL: Brock Purdy pass TD 1+</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="D47" t="n">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="E47" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="48"/>
@@ -1252,7 +1259,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>87% (68%)</t>
+          <t>87% (69%)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1291,7 +1298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>57% (54%)</t>
+          <t>56% (53%)</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1310,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>86% (68%)</t>
+          <t>85% (68%)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>55% (53%)</t>
+          <t>56% (53%)</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1356,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Kirk Cousins</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1366,17 +1373,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kirk Cousins</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>82% (66%)</t>
+          <t>81% (65%)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>49% (49%)</t>
+          <t>48% (49%)</t>
         </is>
       </c>
     </row>
@@ -1388,46 +1395,46 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>81% (65%)</t>
+          <t>80% (65%)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>47% (48%)</t>
+          <t>45% (47%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>80% (65%)</t>
+          <t>78% (64%)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>48% (49%)</t>
+          <t>43% (46%)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>78% (64%)</t>
+          <t>77% (64%)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>42% (46%)</t>
+          <t>41% (45%)</t>
         </is>
       </c>
     </row>
@@ -1439,97 +1446,97 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>78% (64%)</t>
+          <t>76% (63%)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>41% (46%)</t>
+          <t>41% (45%)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>77% (63%)</t>
+          <t>76% (63%)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>41% (45%)</t>
+          <t>39% (45%)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>77% (63%)</t>
+          <t>75% (63%)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>41% (45%)</t>
+          <t>39% (44%)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>75% (63%)</t>
+          <t>68% (59%)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>39% (44%)</t>
+          <t>30% (40%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>74% (62%)</t>
+          <t>67% (59%)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>38% (44%)</t>
+          <t>29% (39%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Patrick Mahomes</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>69% (59%)</t>
+          <t>66% (58%)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30% (40%)</t>
+          <t>29% (39%)</t>
         </is>
       </c>
     </row>
@@ -1541,78 +1548,44 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>68% (59%)</t>
+          <t>66% (58%)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>29% (40%)</t>
+          <t>27% (38%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Malik Willis</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>67% (59%)</t>
+          <t>60% (55%)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28% (39%)</t>
+          <t>22% (36%)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Patrick Mahomes</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>67% (58%)</t>
+          <t>45% (48%)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
-        <is>
-          <t>29% (39%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Malik Willis</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>58% (54%)</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>21% (35%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Daniel Jones</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>45% (47%)</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
         <is>
           <t>11% (31%)</t>
         </is>
@@ -2171,7 +2144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2243,52 +2216,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PIT@NO (INTL neutral site)</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 09:30</t>
+          <t>2026-10-25 13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NO +3.0 / 43.5</t>
+          <t>ATL +2.5 / 49.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PIT 23.1, NO 20.2</t>
+          <t>SF 26.0, ATL 23.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PIT 58% / NO 42%</t>
+          <t>SF 57% / ATL 43%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>43.3</v>
+        <v>49.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PIT 24.6, NO 22.2</t>
+          <t>SF 25.8, ATL 22.4</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>PIT 56%</t>
+          <t>SF 60%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>NO +3.0</t>
+          <t>ATL +3.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2298,42 +2271,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ATL +2.5 / 50.5</t>
+          <t>BAL +3.0 / 46.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SF 26.4, ATL 23.9</t>
+          <t>CIN 24.7, BAL 21.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SF 57% / ATL 43%</t>
+          <t>CIN 58% / BAL 42%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50.4</v>
+        <v>46.4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SF 25.8, ATL 22.5</t>
+          <t>CIN 23.6, BAL 26.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SF 59%</t>
+          <t>CIN 42%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ATL +3.0</t>
+          <t>BAL +3.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2343,42 +2316,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BAL +3.0 / 46.5</t>
+          <t>CAR -3.0 / 44.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CIN 24.8, BAL 21.7</t>
+          <t>TB 20.7, CAR 23.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CIN 58% / BAL 42%</t>
+          <t>TB 41% / CAR 59%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46.5</v>
+        <v>44.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CIN 23.6, BAL 26.4</t>
+          <t>TB 20.6, CAR 25.7</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CIN 42%</t>
+          <t>TB 35%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>BAL +3.0</t>
+          <t>CAR -3.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2388,42 +2361,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CAR -3.0 / 44.5</t>
+          <t>HOU -10.5 / 42.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TB 20.7, CAR 23.7</t>
+          <t>NYG 16.0, HOU 26.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TB 41% / CAR 59%</t>
+          <t>NYG 22% / HOU 78%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44.5</v>
+        <v>42.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TB 20.7, CAR 25.7</t>
+          <t>NYG 19.8, HOU 25.2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TB 36%</t>
+          <t>NYG 35%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CAR -3.0</t>
+          <t>HOU -10.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>IND@MIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2433,42 +2406,42 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HOU -10.5 / 42.5</t>
+          <t>MIN -6.5 / 41.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NYG 16.0, HOU 26.4</t>
+          <t>IND 17.4, MIN 23.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NYG 21% / HOU 79%</t>
+          <t>IND 30% / MIN 70%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>42.4</v>
+        <v>41.3</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NYG 19.8, HOU 25.2</t>
+          <t>IND 20.5, MIN 24.4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>NYG 35%</t>
+          <t>IND 38%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>HOU -10.0</t>
+          <t>MIN -7.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IND@MIN</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2478,42 +2451,42 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MIN -6.5 / 41.5</t>
+          <t>NYJ -3.5 / 39.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IND 17.4, MIN 24.1</t>
+          <t>MIA 17.8, NYJ 21.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IND 30% / MIN 70%</t>
+          <t>MIA 39% / NYJ 61%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>41.5</v>
+        <v>39.3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>IND 20.7, MIN 24.4</t>
+          <t>MIA 18.7, NYJ 22.1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>IND 39%</t>
+          <t>MIA 40%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MIN -7.0</t>
+          <t>NYJ -3.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIA@NYJ</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2523,132 +2496,132 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NYJ -4.5 / 39.5</t>
+          <t>TEN +2.5 / 36.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIA 17.4, NYJ 22.0</t>
+          <t>CLE 19.5, TEN 16.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MIA 37% / NYJ 63%</t>
+          <t>CLE 58% / TEN 42%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>39.4</v>
+        <v>36.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MIA 18.8, NYJ 22.1</t>
+          <t>CLE 18.9, TEN 17.8</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MIA 40%</t>
+          <t>CLE 53%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NYJ -4.0</t>
+          <t>TEN +3.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 13:00</t>
+          <t>2026-10-25 16:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TEN +1.5 / 36.5</t>
+          <t>ARI +4.5 / 42.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE 18.9, TEN 17.5</t>
+          <t>DEN 23.5, ARI 19.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CLE 54% / TEN 46%</t>
+          <t>DEN 63% / ARI 37%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>36.3</v>
+        <v>42.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CLE 19.1, TEN 17.8</t>
+          <t>DEN 23.4, ARI 21.2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CLE 54%</t>
+          <t>DEN 57%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TEN +1.0</t>
+          <t>ARI +4.0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 16:05</t>
+          <t>2026-10-25 16:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ARI +4.5 / 43.5</t>
+          <t>DET -3.5 / 55.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DEN 24.0, ARI 19.4</t>
+          <t>GB 26.0, DET 29.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DEN 63% / ARI 37%</t>
+          <t>GB 41% / DET 59%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>43.4</v>
+        <v>55.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DEN 23.3, ARI 21.1</t>
+          <t>GB 22.8, DET 27.9</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DEN 56%</t>
+          <t>GB 36%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ARI +4.0</t>
+          <t>DET -3.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2658,176 +2631,131 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DET -3.5 / 55.5</t>
+          <t>LV +3.5 / 48.5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GB 26.0, DET 29.4</t>
+          <t>LA 25.8, LV 22.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GB 41% / DET 59%</t>
+          <t>LA 60% / LV 40%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>55.4</v>
+        <v>48.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GB 22.8, DET 27.9</t>
+          <t>LA 24.9, LV 23.2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>GB 36%</t>
+          <t>LA 55%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DET -3.0</t>
+          <t>LV +4.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 16:25</t>
+          <t>2026-10-25 20:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LV +3.0 / 48.5</t>
+          <t>SEA -3.0 / 42.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA 25.7, LV 22.8</t>
+          <t>KC 19.7, SEA 22.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LA 59% / LV 41%</t>
+          <t>KC 41% / SEA 59%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>48.6</v>
+        <v>42.4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>LA 24.8, LV 23.3</t>
+          <t>KC 21.5, SEA 24.1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>LA 55%</t>
+          <t>KC 42%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LV +3.0</t>
+          <t>SEA -3.0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 20:20</t>
+          <t>2026-10-26 20:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SEA -3.0 / 42.5</t>
+          <t>PHI +4.5 / 43.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KC 19.7, SEA 22.7</t>
+          <t>DAL 23.8, PHI 19.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KC 42% / SEA 58%</t>
+          <t>DAL 62% / PHI 38%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>42.4</v>
+        <v>43.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>KC 21.6, SEA 24.2</t>
+          <t>DAL 23.1, PHI 23.9</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KC 43%</t>
+          <t>DAL 47%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SEA -3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-26 20:15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PHI +4.5 / 43.5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DAL 24.1, PHI 19.5</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>DAL 63% / PHI 37%</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DAL 23.1, PHI 23.9</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>DAL 47%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>PHI +4.0</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Already played: NE@CHI final NE 24, CHI 30 (market CHI -3.0, total 50.5; projected 23.7-26.7).</t>
         </is>
@@ -8369,13 +8297,13 @@
         <v>20.4</v>
       </c>
       <c r="F6" t="n">
-        <v>217.3</v>
+        <v>217.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="I6" t="n">
         <v>0.21</v>
@@ -8384,10 +8312,10 @@
         <v>0.19</v>
       </c>
       <c r="K6" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="L6" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -8410,28 +8338,28 @@
         <v>0.98</v>
       </c>
       <c r="E7" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="F7" t="n">
-        <v>288.7</v>
+        <v>289.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="L7" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8">
@@ -8457,7 +8385,7 @@
         <v>23.7</v>
       </c>
       <c r="F8" t="n">
-        <v>257.1</v>
+        <v>256.4</v>
       </c>
       <c r="G8" t="n">
         <v>1.84</v>
@@ -8501,25 +8429,25 @@
         <v>22.2</v>
       </c>
       <c r="F9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G9" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>0.11</v>
       </c>
       <c r="K9" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="L9" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="10">
@@ -8542,28 +8470,28 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="F10" t="n">
-        <v>238.9</v>
+        <v>234.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="I10" t="n">
         <v>0.23</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K10" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="L10" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -8589,25 +8517,25 @@
         <v>23.3</v>
       </c>
       <c r="F11" t="n">
-        <v>244.7</v>
+        <v>242.3</v>
       </c>
       <c r="G11" t="n">
         <v>1.66</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
         <v>0.11</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="K11" t="n">
         <v>10.6</v>
       </c>
       <c r="L11" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="12">
@@ -8630,28 +8558,28 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F12" t="n">
-        <v>212.5</v>
+        <v>213.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="I12" t="n">
         <v>0.23</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K12" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="L12" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="13">
@@ -8674,16 +8602,16 @@
         <v>0.98</v>
       </c>
       <c r="E13" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="F13" t="n">
-        <v>252.5</v>
+        <v>244.8</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>0.14</v>
@@ -8695,7 +8623,7 @@
         <v>10.2</v>
       </c>
       <c r="L13" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="14">
@@ -8721,13 +8649,13 @@
         <v>20.4</v>
       </c>
       <c r="F14" t="n">
-        <v>225.6</v>
+        <v>226.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
         <v>0.04</v>
@@ -8736,54 +8664,54 @@
         <v>0.04</v>
       </c>
       <c r="K14" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L14" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>22.4</v>
+        <v>16.8</v>
       </c>
       <c r="F15" t="n">
-        <v>242.5</v>
+        <v>195.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.55</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="K15" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="L15" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="16">
@@ -8809,13 +8737,13 @@
         <v>23.9</v>
       </c>
       <c r="F16" t="n">
-        <v>258.7</v>
+        <v>258.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>0.15</v>
@@ -8824,54 +8752,54 @@
         <v>0.14</v>
       </c>
       <c r="K16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>16.7</v>
+        <v>19.3</v>
       </c>
       <c r="F17" t="n">
-        <v>190.7</v>
+        <v>216.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="H17" t="n">
-        <v>14.2</v>
+        <v>6.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="L17" t="n">
-        <v>14.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="18">
@@ -8900,66 +8828,66 @@
         <v>197.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="K18" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="F19" t="n">
-        <v>217</v>
+        <v>229.9</v>
       </c>
       <c r="G19" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
-        <v>6.5</v>
+        <v>8.9</v>
       </c>
       <c r="I19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="K19" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="L19" t="n">
-        <v>13.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="20"/>
@@ -9065,19 +8993,19 @@
         <v>20</v>
       </c>
       <c r="F23" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>30.6</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0.78</v>
@@ -9086,7 +9014,7 @@
         <v>8.4</v>
       </c>
       <c r="M23" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N23" t="n">
         <v>24.6</v>
@@ -9115,31 +9043,31 @@
         <v>14.4</v>
       </c>
       <c r="F24" t="n">
-        <v>66.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="H24" t="n">
         <v>6.5</v>
       </c>
       <c r="I24" t="n">
-        <v>53.9</v>
+        <v>54.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="L24" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="N24" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="25">
@@ -9162,10 +9090,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="F25" t="n">
-        <v>101.4</v>
+        <v>101.6</v>
       </c>
       <c r="G25" t="n">
         <v>0.8100000000000001</v>
@@ -9186,10 +9114,10 @@
         <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N25" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="26">
@@ -9215,7 +9143,7 @@
         <v>13.4</v>
       </c>
       <c r="F26" t="n">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="G26" t="n">
         <v>0.63</v>
@@ -9236,10 +9164,10 @@
         <v>5.9</v>
       </c>
       <c r="M26" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N26" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="27">
@@ -9265,7 +9193,7 @@
         <v>13.7</v>
       </c>
       <c r="F27" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
         <v>0.77</v>
@@ -9274,7 +9202,7 @@
         <v>2.7</v>
       </c>
       <c r="I27" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="J27" t="n">
         <v>0.1</v>
@@ -9283,10 +9211,10 @@
         <v>0.6</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M27" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="N27" t="n">
         <v>15</v>
@@ -9315,16 +9243,16 @@
         <v>18.6</v>
       </c>
       <c r="F28" t="n">
-        <v>80.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="H28" t="n">
         <v>1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="J28" t="n">
         <v>0.1</v>
@@ -9333,13 +9261,13 @@
         <v>0.59</v>
       </c>
       <c r="L28" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="N28" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="29">
@@ -9362,10 +9290,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="F29" t="n">
-        <v>58.7</v>
+        <v>57.8</v>
       </c>
       <c r="G29" t="n">
         <v>0.53</v>
@@ -9374,22 +9302,22 @@
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>26.4</v>
+        <v>25.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0.53</v>
       </c>
       <c r="L29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M29" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N29" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="30">
@@ -9412,10 +9340,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F30" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="G30" t="n">
         <v>0.53</v>
@@ -9424,7 +9352,7 @@
         <v>3.4</v>
       </c>
       <c r="I30" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
         <v>0.18</v>
@@ -9439,7 +9367,7 @@
         <v>19.8</v>
       </c>
       <c r="N30" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="31">
@@ -9465,16 +9393,16 @@
         <v>18.2</v>
       </c>
       <c r="F31" t="n">
-        <v>94.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="J31" t="n">
         <v>0.04</v>
@@ -9512,34 +9440,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F32" t="n">
-        <v>59.9</v>
+        <v>59.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="H32" t="n">
         <v>3.7</v>
       </c>
       <c r="I32" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="J32" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="L32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="M32" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="N32" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="33">
@@ -9565,7 +9493,7 @@
         <v>15</v>
       </c>
       <c r="F33" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="G33" t="n">
         <v>0.48</v>
@@ -9595,51 +9523,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="F34" t="n">
-        <v>74.5</v>
+        <v>76.7</v>
       </c>
       <c r="G34" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="I34" t="n">
-        <v>35.7</v>
+        <v>17.8</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="L34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M34" t="n">
-        <v>18.4</v>
+        <v>15</v>
       </c>
       <c r="N34" t="n">
-        <v>18.2</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="35">
@@ -9665,31 +9593,31 @@
         <v>13.4</v>
       </c>
       <c r="F35" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J35" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="L35" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="M35" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="N35" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="36">
@@ -9712,10 +9640,10 @@
         <v>0.95</v>
       </c>
       <c r="E36" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="F36" t="n">
-        <v>66.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0.44</v>
@@ -9724,7 +9652,7 @@
         <v>1.9</v>
       </c>
       <c r="I36" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="J36" t="n">
         <v>0.11</v>
@@ -9736,210 +9664,210 @@
         <v>3.2</v>
       </c>
       <c r="M36" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="N36" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>16.2</v>
+        <v>15.5</v>
       </c>
       <c r="F37" t="n">
-        <v>72.8</v>
+        <v>59.9</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="H37" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="I37" t="n">
-        <v>17.1</v>
+        <v>8.6</v>
       </c>
       <c r="J37" t="n">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="L37" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M37" t="n">
-        <v>14.4</v>
+        <v>11.2</v>
       </c>
       <c r="N37" t="n">
-        <v>14.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E38" t="n">
-        <v>15.5</v>
+        <v>17.8</v>
       </c>
       <c r="F38" t="n">
-        <v>59.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0.47</v>
       </c>
       <c r="H38" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="n">
-        <v>8.6</v>
+        <v>20.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="L38" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>11.2</v>
+        <v>15.7</v>
       </c>
       <c r="N38" t="n">
-        <v>11</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Dameon Pierce</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>17.8</v>
+        <v>12.6</v>
       </c>
       <c r="F39" t="n">
-        <v>77.40000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="I39" t="n">
-        <v>20.6</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="M39" t="n">
-        <v>15.7</v>
+        <v>13.4</v>
       </c>
       <c r="N39" t="n">
-        <v>14.8</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dameon Pierce</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="F40" t="n">
-        <v>50.6</v>
+        <v>29.9</v>
       </c>
       <c r="G40" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H40" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="I40" t="n">
-        <v>24.1</v>
+        <v>14.2</v>
       </c>
       <c r="J40" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="L40" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>13.4</v>
+        <v>8.9</v>
       </c>
       <c r="N40" t="n">
-        <v>13.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="41"/>
@@ -10038,22 +9966,22 @@
         <v>6.5</v>
       </c>
       <c r="G44" t="n">
-        <v>67.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="J44" t="n">
         <v>3.8</v>
       </c>
       <c r="K44" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="L44" t="n">
         <v>17</v>
-      </c>
-      <c r="L44" t="n">
-        <v>16.9</v>
       </c>
     </row>
     <row r="45">
@@ -10085,7 +10013,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0.47</v>
@@ -10094,10 +10022,10 @@
         <v>3.5</v>
       </c>
       <c r="K45" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="L45" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="46">
@@ -10120,13 +10048,13 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
         <v>7</v>
       </c>
       <c r="G46" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="H46" t="n">
         <v>0.5600000000000001</v>
@@ -10164,13 +10092,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="G47" t="n">
-        <v>66.7</v>
+        <v>66</v>
       </c>
       <c r="H47" t="n">
         <v>0.49</v>
@@ -10179,13 +10107,13 @@
         <v>0.4</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K47" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="L47" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="48">
@@ -10214,13 +10142,13 @@
         <v>5.1</v>
       </c>
       <c r="G48" t="n">
-        <v>89.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="J48" t="n">
         <v>2.9</v>
@@ -10235,33 +10163,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>10.7</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="G49" t="n">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H49" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0.36</v>
@@ -10270,42 +10198,42 @@
         <v>2.6</v>
       </c>
       <c r="K49" t="n">
-        <v>17.6</v>
+        <v>15.3</v>
       </c>
       <c r="L49" t="n">
-        <v>17.6</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D50" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="F50" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="G50" t="n">
-        <v>76.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="H50" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0.35</v>
@@ -10314,10 +10242,10 @@
         <v>2.5</v>
       </c>
       <c r="K50" t="n">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="L50" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="51">
@@ -10340,13 +10268,13 @@
         <v>0.96</v>
       </c>
       <c r="E51" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F51" t="n">
         <v>4.8</v>
       </c>
       <c r="G51" t="n">
-        <v>66.09999999999999</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="H51" t="n">
         <v>0.37</v>
@@ -10358,10 +10286,10 @@
         <v>2.4</v>
       </c>
       <c r="K51" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="L51" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="52">
@@ -10384,57 +10312,57 @@
         <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F52" t="n">
         <v>5.2</v>
       </c>
       <c r="G52" t="n">
-        <v>75.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="J52" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K52" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="L52" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Justin Jefferson</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E53" t="n">
-        <v>9.9</v>
+        <v>7.1</v>
       </c>
       <c r="F53" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="G53" t="n">
-        <v>71.3</v>
+        <v>60.1</v>
       </c>
       <c r="H53" t="n">
         <v>0.37</v>
@@ -10443,362 +10371,362 @@
         <v>0.32</v>
       </c>
       <c r="J53" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="K53" t="n">
-        <v>15.1</v>
+        <v>12.8</v>
       </c>
       <c r="L53" t="n">
-        <v>15</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Chris Olave</t>
+          <t>Zay Flowers</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="D54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>9.4</v>
+        <v>7.9</v>
       </c>
       <c r="F54" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="G54" t="n">
-        <v>70.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="H54" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="J54" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>14.9</v>
+        <v>15.6</v>
       </c>
       <c r="L54" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D55" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="F55" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>50.7</v>
+        <v>39.8</v>
       </c>
       <c r="H55" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J55" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
       <c r="L55" t="n">
-        <v>11.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Justin Jefferson</t>
+          <t>Jalen Coker</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="F56" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G56" t="n">
-        <v>58.3</v>
+        <v>55.8</v>
       </c>
       <c r="H56" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="J56" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="L56" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Tee Higgins</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="G57" t="n">
-        <v>39.7</v>
+        <v>66.2</v>
       </c>
       <c r="H57" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K57" t="n">
-        <v>9</v>
+        <v>13.4</v>
       </c>
       <c r="L57" t="n">
-        <v>8.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Jaylen Waddle</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E58" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="F58" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G58" t="n">
-        <v>57</v>
+        <v>52.4</v>
       </c>
       <c r="H58" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>0.28</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K58" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="L58" t="n">
-        <v>12.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Zay Flowers</t>
+          <t>Garrett Wilson</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="F59" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>76</v>
+        <v>58.2</v>
       </c>
       <c r="H59" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K59" t="n">
-        <v>14.9</v>
+        <v>12.6</v>
       </c>
       <c r="L59" t="n">
-        <v>14.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Garrett Wilson</t>
+          <t>Puka Nacua</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>10.7</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="G60" t="n">
-        <v>58.5</v>
+        <v>91.2</v>
       </c>
       <c r="H60" t="n">
-        <v>0.32</v>
+        <v>0.55</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="J60" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K60" t="n">
-        <v>12.7</v>
+        <v>19.9</v>
       </c>
       <c r="L60" t="n">
-        <v>12.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tee Higgins</t>
+          <t>George Pickens</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D61" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E61" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="G61" t="n">
-        <v>67.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="H61" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="I61" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J61" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K61" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="L61" t="n">
         <v>13.5</v>
@@ -10807,265 +10735,265 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jaylen Waddle</t>
+          <t>Wan'Dale Robinson</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D62" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="F62" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="G62" t="n">
-        <v>51.9</v>
+        <v>47.4</v>
       </c>
       <c r="H62" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J62" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K62" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="L62" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>George Pickens</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D63" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>8.800000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="F63" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="G63" t="n">
-        <v>71.5</v>
+        <v>46</v>
       </c>
       <c r="H63" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="I63" s="6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J63" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K63" t="n">
-        <v>14.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>13.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Puka Nacua</t>
+          <t>Malik Nabers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="D64" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>10.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>91.09999999999999</v>
+        <v>64</v>
       </c>
       <c r="H64" t="n">
-        <v>0.55</v>
+        <v>0.27</v>
       </c>
       <c r="I64" s="6" t="n">
-        <v>0.46</v>
+        <v>0.24</v>
       </c>
       <c r="J64" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K64" t="n">
-        <v>19.9</v>
+        <v>13</v>
       </c>
       <c r="L64" t="n">
-        <v>9.9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Darius Cooper</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="D65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.7</v>
+        <v>2.7</v>
       </c>
       <c r="F65" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="G65" t="n">
-        <v>45.8</v>
+        <v>21.5</v>
       </c>
       <c r="H65" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="I65" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J65" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K65" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="L65" t="n">
-        <v>9.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Malik Nabers</t>
+          <t>Michael Wilson</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D66" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G66" t="n">
-        <v>65.90000000000001</v>
+        <v>48.8</v>
       </c>
       <c r="H66" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I66" s="6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="J66" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K66" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="L66" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Wan'Dale Robinson</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
           <t>TEN</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="D67" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E67" t="n">
-        <v>7.3</v>
+        <v>6.2</v>
       </c>
       <c r="F67" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="G67" t="n">
-        <v>42.7</v>
+        <v>43.9</v>
       </c>
       <c r="H67" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="J67" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K67" t="n">
         <v>10.2</v>
       </c>
       <c r="L67" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="68"/>
@@ -11158,28 +11086,28 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="F71" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="G71" t="n">
         <v>77.40000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="I71" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="J71" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K71" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="L71" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="72">
@@ -11202,10 +11130,10 @@
         <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G72" t="n">
         <v>57.3</v>
@@ -11223,7 +11151,7 @@
         <v>14.2</v>
       </c>
       <c r="L72" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="73">
@@ -11246,28 +11174,28 @@
         <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="F73" t="n">
         <v>4.9</v>
       </c>
       <c r="G73" t="n">
-        <v>56.8</v>
+        <v>57.3</v>
       </c>
       <c r="H73" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="J73" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K73" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="L73" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="74">
@@ -11290,16 +11218,16 @@
         <v>0.95</v>
       </c>
       <c r="E74" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="F74" t="n">
         <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>66.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="H74" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I74" s="6" t="n">
         <v>0.37</v>
@@ -11308,7 +11236,7 @@
         <v>2.6</v>
       </c>
       <c r="K74" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="L74" t="n">
         <v>14.5</v>
@@ -11317,89 +11245,89 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Colby Parkinson</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ARI</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D75" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E75" t="n">
-        <v>11.8</v>
+        <v>5.9</v>
       </c>
       <c r="F75" t="n">
-        <v>7.7</v>
+        <v>4</v>
       </c>
       <c r="G75" t="n">
-        <v>66.5</v>
+        <v>42.2</v>
       </c>
       <c r="H75" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="J75" t="n">
         <v>2.3</v>
       </c>
       <c r="K75" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="L75" t="n">
-        <v>16.6</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Colby Parkinson</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>ARI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D76" s="6" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>5.9</v>
+        <v>11.8</v>
       </c>
       <c r="F76" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="G76" t="n">
-        <v>42.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="I76" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="J76" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K76" t="n">
-        <v>10.7</v>
+        <v>16.5</v>
       </c>
       <c r="L76" t="n">
-        <v>10.1</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="77">
@@ -11422,13 +11350,13 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="F77" t="n">
         <v>4.7</v>
       </c>
       <c r="G77" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="H77" t="n">
         <v>0.34</v>
@@ -11443,7 +11371,7 @@
         <v>12</v>
       </c>
       <c r="L77" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="78">
@@ -11472,22 +11400,22 @@
         <v>5.3</v>
       </c>
       <c r="G78" t="n">
-        <v>55</v>
+        <v>55.2</v>
       </c>
       <c r="H78" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I78" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K78" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="L78" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="79">
@@ -11516,22 +11444,22 @@
         <v>3.4</v>
       </c>
       <c r="G79" t="n">
-        <v>32.8</v>
+        <v>32.6</v>
       </c>
       <c r="H79" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K79" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="L79" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="80">
@@ -11554,13 +11482,13 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F80" t="n">
         <v>5.7</v>
       </c>
       <c r="G80" t="n">
-        <v>62.1</v>
+        <v>60.2</v>
       </c>
       <c r="H80" t="n">
         <v>0.31</v>
@@ -11572,193 +11500,193 @@
         <v>1.9</v>
       </c>
       <c r="K80" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="L80" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D81" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="F81" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="G81" t="n">
-        <v>42.9</v>
+        <v>29.5</v>
       </c>
       <c r="H81" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="J81" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K81" t="n">
-        <v>10.3</v>
+        <v>7.8</v>
       </c>
       <c r="L81" t="n">
-        <v>10.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Juwan Johnson</t>
+          <t>Dalton Schultz</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYG</t>
         </is>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E82" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="F82" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
-        <v>42.2</v>
+        <v>37.3</v>
       </c>
       <c r="H82" t="n">
         <v>0.3</v>
       </c>
       <c r="I82" s="6" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="J82" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K82" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="L82" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Dalton Schultz</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>NYG</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D83" s="6" t="n">
         <v>0.95</v>
       </c>
       <c r="E83" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G83" t="n">
-        <v>37.5</v>
+        <v>34.4</v>
       </c>
       <c r="H83" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="I83" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J83" t="n">
         <v>1.7</v>
       </c>
       <c r="K83" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Travis Kelce</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
           <t>SEA</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="D84" s="6" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="E84" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="F84" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="G84" t="n">
-        <v>29.5</v>
+        <v>55.2</v>
       </c>
       <c r="H84" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="I84" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J84" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K84" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="L84" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85"/>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.3; SF 7.9; HOU 7.9; GB 7.8; LA 7.8; CIN 7.6; DAL 7.5; MIN 7.5; DEN 7.5; ATL 7.5</t>
+          <t>Kickers (this league: FG 3, XP 1; ranked by team implied points, the only validated signal; differences are within noise): DET 8.3; HOU 7.9; SF 7.8; GB 7.8; LA 7.8; CIN 7.6; MIN 7.5; DAL 7.5; CAR 7.5; DEN 7.5</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11713,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="49" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11915,16 +11843,16 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.655</v>
       </c>
       <c r="G6" t="n">
-        <v>-199</v>
+        <v>-190</v>
       </c>
       <c r="H6" t="n">
-        <v>-147</v>
+        <v>-141</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>1</v>
@@ -11953,10 +11881,10 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.652</v>
+        <v>0.6509999999999999</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.652</v>
+        <v>0.6509999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-187</v>
@@ -11991,16 +11919,16 @@
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.648</v>
       </c>
       <c r="G8" t="n">
-        <v>-183</v>
+        <v>-184</v>
       </c>
       <c r="H8" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>1</v>
@@ -12029,10 +11957,10 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.601</v>
+        <v>0.602</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.601</v>
+        <v>0.602</v>
       </c>
       <c r="G9" t="n">
         <v>-151</v>
@@ -12045,7 +11973,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>opp QB: fill-in QB (Tanner McKee)</t>
+          <t>opp QB: fill-in QB (Tanner McKee) red-team downgrade</t>
         </is>
       </c>
     </row>
@@ -12087,7 +12015,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>opp QB: fill-in QB (J.J. McCarthy)</t>
+          <t>opp QB: fill-in QB (J.J. McCarthy) red-team downgrade</t>
         </is>
       </c>
     </row>
@@ -12113,16 +12041,16 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.556</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.556</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-125</v>
+        <v>-122</v>
       </c>
       <c r="H11" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>1</v>
@@ -12151,23 +12079,23 @@
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0.528</v>
+        <v>0.525</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.528</v>
+        <v>0.525</v>
       </c>
       <c r="G12" t="n">
-        <v>-112</v>
+        <v>-111</v>
       </c>
       <c r="H12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>opp QB: fill-in QB (QB1 Out)</t>
+          <t>opp QB: fill-in QB (QB1 Out) red-team downgrade</t>
         </is>
       </c>
     </row>
@@ -12193,13 +12121,13 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0.52</v>
+        <v>0.522</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>0.52</v>
+        <v>0.522</v>
       </c>
       <c r="G13" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H13" t="n">
         <v>115</v>
@@ -12231,16 +12159,16 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.507</v>
+        <v>0.512</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.507</v>
+        <v>0.512</v>
       </c>
       <c r="G14" t="n">
-        <v>-103</v>
+        <v>-105</v>
       </c>
       <c r="H14" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>1</v>
@@ -12254,35 +12182,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ashton Jeanty</t>
+          <t>Amon-Ra St. Brown</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>0.476</v>
+        <v>0.482</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.476</v>
+        <v>0.482</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H15" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>1</v>
@@ -12292,35 +12220,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Ashton Jeanty</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>0.474</v>
+        <v>0.464</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.474</v>
+        <v>0.464</v>
       </c>
       <c r="G16" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H16" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>1</v>
@@ -12349,16 +12277,16 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0.475</v>
+        <v>0.477</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0.452</v>
+        <v>0.454</v>
       </c>
       <c r="G17" t="n">
         <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0.95</v>
@@ -12391,16 +12319,16 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.466</v>
+        <v>0.472</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.446</v>
+        <v>0.452</v>
       </c>
       <c r="G18" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H18" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0.96</v>
@@ -12410,35 +12338,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jaylen Warren</t>
+          <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.4379999999999999</v>
+        <v>0.436</v>
       </c>
       <c r="G19" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H19" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>1</v>
@@ -12448,35 +12376,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jaxon Smith-Njigba</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.425</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.4370000000000001</v>
+        <v>0.425</v>
       </c>
       <c r="G20" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H20" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>1</v>
@@ -12505,16 +12433,16 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.422</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.4320000000000001</v>
+        <v>0.422</v>
       </c>
       <c r="G21" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H21" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>1</v>
@@ -12524,17 +12452,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -12543,21 +12471,25 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>0.417</v>
+        <v>0.436</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.417</v>
+        <v>0.415</v>
       </c>
       <c r="G22" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H22" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>0.95</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>opp QB: QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12581,16 +12513,16 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>0.415</v>
+        <v>0.411</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.415</v>
+        <v>0.411</v>
       </c>
       <c r="G23" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H23" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>1</v>
@@ -12600,17 +12532,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Jonathan Taylor</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -12619,25 +12551,21 @@
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0.436</v>
+        <v>0.418</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.415</v>
+        <v>0.397</v>
       </c>
       <c r="G24" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H24" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0.95</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>opp QB: QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12661,16 +12589,16 @@
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.398</v>
+        <v>0.396</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0.398</v>
+        <v>0.396</v>
       </c>
       <c r="G25" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="H25" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>1</v>
@@ -12684,111 +12612,111 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jonathan Taylor</t>
+          <t>Christian Watson</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>0.416</v>
+        <v>0.402</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.396</v>
+        <v>0.385</v>
       </c>
       <c r="G26" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="H26" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Christian Watson</t>
+          <t>Sam LaPorta</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DET</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.407</v>
+        <v>0.383</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.389</v>
+        <v>0.383</v>
       </c>
       <c r="G27" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="H27" t="n">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sam LaPorta</t>
+          <t>Tucker Kraft</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>0.382</v>
+        <v>0.377</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>0.382</v>
+        <v>0.377</v>
       </c>
       <c r="G28" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H28" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>1</v>
@@ -12817,16 +12745,16 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>0.371</v>
+        <v>0.365</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0.371</v>
+        <v>0.365</v>
       </c>
       <c r="G29" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H29" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>1</v>
@@ -12840,35 +12768,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tucker Kraft</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.368</v>
+        <v>0.357</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.368</v>
+        <v>0.357</v>
       </c>
       <c r="G30" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="H30" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>1</v>
@@ -12878,82 +12806,82 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Tetairoa McMillan</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NYJ</t>
+          <t>CAR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.362</v>
+        <v>0.357</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.362</v>
+        <v>0.357</v>
       </c>
       <c r="G31" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H31" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>opp QB: QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CeeDee Lamb</t>
+          <t>Ollie Gordon II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NYJ</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.359</v>
+        <v>0.353</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.359</v>
+        <v>0.353</v>
       </c>
       <c r="G32" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H32" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>opp QB: fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12977,16 +12905,16 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.373</v>
+        <v>0.368</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.354</v>
+        <v>0.349</v>
       </c>
       <c r="G33" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="H33" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0.95</v>
@@ -12996,17 +12924,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Tetairoa McMillan</t>
+          <t>CeeDee Lamb</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CAR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -13015,23 +12943,23 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="G34" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H34" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>opp QB: QB1 designation (start probability 65%)</t>
+          <t>opp QB: fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
@@ -13110,10 +13038,10 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.276</v>
+        <v>0.265</v>
       </c>
       <c r="E39" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40">
@@ -13133,10 +13061,10 @@
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>0.264</v>
+        <v>0.261</v>
       </c>
       <c r="E40" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41">
@@ -13156,10 +13084,10 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>0.257</v>
+        <v>0.255</v>
       </c>
       <c r="E41" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42">
@@ -13182,7 +13110,7 @@
         <v>0.215</v>
       </c>
       <c r="E42" t="n">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="43">
@@ -13202,10 +13130,10 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>0.205</v>
+        <v>0.203</v>
       </c>
       <c r="E43" t="n">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44">
@@ -13225,10 +13153,10 @@
         </is>
       </c>
       <c r="D44" s="6" t="n">
-        <v>0.183</v>
+        <v>0.174</v>
       </c>
       <c r="E44" t="n">
-        <v>447</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45">
@@ -13248,10 +13176,10 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>0.162</v>
+        <v>0.161</v>
       </c>
       <c r="E45" t="n">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
     <row r="46">
@@ -13271,10 +13199,10 @@
         </is>
       </c>
       <c r="D46" s="6" t="n">
-        <v>0.159</v>
+        <v>0.155</v>
       </c>
       <c r="E46" t="n">
-        <v>530</v>
+        <v>544</v>
       </c>
     </row>
     <row r="47">
@@ -13355,7 +13283,7 @@
         <v>0.218</v>
       </c>
       <c r="E51" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52">
@@ -13375,10 +13303,10 @@
         </is>
       </c>
       <c r="D52" s="6" t="n">
-        <v>0.197</v>
+        <v>0.196</v>
       </c>
       <c r="E52" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53">
@@ -13401,7 +13329,7 @@
         <v>0.182</v>
       </c>
       <c r="E53" t="n">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="54">
@@ -13421,10 +13349,10 @@
         </is>
       </c>
       <c r="D54" s="6" t="n">
-        <v>0.176</v>
+        <v>0.177</v>
       </c>
       <c r="E54" t="n">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="55">
@@ -13447,7 +13375,7 @@
         <v>0.174</v>
       </c>
       <c r="E55" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56">
@@ -13467,10 +13395,10 @@
         </is>
       </c>
       <c r="D56" s="6" t="n">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="E56" t="n">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57">
@@ -13493,53 +13421,53 @@
         <v>0.16</v>
       </c>
       <c r="E57" t="n">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Aaron Jones</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D58" s="6" t="n">
-        <v>0.142</v>
+        <v>0.143</v>
       </c>
       <c r="E58" t="n">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Aaron Jones</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="D59" s="6" t="n">
-        <v>0.138</v>
+        <v>0.142</v>
       </c>
       <c r="E59" t="n">
-        <v>624</v>
+        <v>603</v>
       </c>
     </row>
     <row r="60">
@@ -13559,17 +13487,17 @@
         </is>
       </c>
       <c r="D60" s="6" t="n">
-        <v>0.135</v>
+        <v>0.136</v>
       </c>
       <c r="E60" t="n">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="61"/>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Alvin Kamara (NO) 25% fair +303, take at +351+; George Holani (SEA) 25% fair +306, take at +354+; Malik Nabers (NYG) 25% fair +307, take at +356+; Tre Tucker (LV) 24% fair +309, take at +358+; Samaje Perine (CIN) 24% fair +312, take at +361+; Michael Wilson (ARI) 24% fair +319, take at +370+; Travis Kelce (KC) 25% fair +304, take at +352+; Mike Gesicki (CIN) 24% fair +323, take at +373+; Wan'Dale Robinson (TEN) 24% fair +323, take at +374+; Darnell Washington (PIT) 23% fair +330, take at +382+; Jahan Dotson (ATL) 23% fair +344, take at +398+; Darius Cooper (PHI) 22% fair +347, take at +400+; Ryan Flournoy (DAL) 22% fair +348, take at +401+; Darren Waller (CAR) 24% fair +324, take at +375+; Xavier Worthy (KC) 22% fair +350, take at +403+; Kaelon Black (SF) 22% fair +354, take at +409+; Jameson Williams (DET) 22% fair +358, take at +413+; Devaughn Vele (NO) 22% fair +358, take at +413+; KC Concepcion (CLE) 23% fair +337, take at +389+; Carnell Tate (TEN) 22% fair +362, take at +417+</t>
+          <t>Sneaky longshots (8% to 25% anytime, active 90%+): Tre Tucker (LV) 25% fair +301, take at +349+; George Holani (SEA) 25% fair +305, take at +354+; Samaje Perine (CIN) 24% fair +310, take at +359+; Malik Nabers (NYG) 24% fair +317, take at +367+; Darius Cooper (PHI) 23% fair +327, take at +379+; Travis Kelce (KC) 24% fair +310, take at +359+; Michael Wilson (ARI) 23% fair +330, take at +382+; Mike Gesicki (CIN) 23% fair +339, take at +392+; Xavier Worthy (KC) 22% fair +347, take at +401+; Malik Washington (MIA) 22% fair +350, take at +404+; Jameson Williams (DET) 22% fair +351, take at +405+; KC Concepcion (CLE) 23% fair +328, take at +380+; Darren Waller (CAR) 23% fair +329, take at +381+; Ryan Flournoy (DAL) 22% fair +357, take at +411+; Carnell Tate (TEN) 22% fair +357, take at +411+; Kaelon Black (SF) 22% fair +365, take at +421+; Harold Fannin Jr. (CLE) 22% fair +365, take at +421+; Jahan Dotson (ATL) 21% fair +367, take at +423+; Cade Otton (TB) 21% fair +368, take at +424+; Brandin Cooks (SF) 21% fair +368, take at +424+</t>
         </is>
       </c>
     </row>
@@ -13584,12 +13512,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -13613,7 +13541,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>484 lines screened: 23 PLAY (14 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 78 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
+          <t>451 lines screened: 17 PLAY (9 receiving, tagged thin: W6 receiving lines hit 35 to 52 percent, Thursday 7 of 11), 73 LEAN (the 25 best shown). Pulled by rule: receiving LEANs, pass-volume UNDERs, UNDERs on a teammate of a player now Out or Questionable ('role change'). PLAY = shrunk probability about 55.4%+ (about 61% raw), active 95%+, side cleared in at least half of the player's games. 'Agree' = the model-only track picks the same side.</t>
         </is>
       </c>
     </row>
@@ -13692,26 +13620,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IND@MIN</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kyler Murray</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>26.5</v>
+        <v>11.5</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>0.83</v>
@@ -13720,11 +13648,11 @@
         <v>0.67</v>
       </c>
       <c r="I5" t="n">
-        <v>-200</v>
+        <v>-199</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -13733,7 +13661,11 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -13743,39 +13675,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>IND@MIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Kyler Murray</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11.5</v>
+        <v>25.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="I6" t="n">
-        <v>-200</v>
+        <v>-191</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -13784,11 +13716,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -13820,13 +13748,13 @@
         <v>11.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="I7" t="n">
-        <v>-172</v>
+        <v>-177</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -13875,13 +13803,13 @@
         <v>2.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I8" t="n">
-        <v>-171</v>
+        <v>-173</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -13926,13 +13854,13 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="I9" t="n">
-        <v>-170</v>
+        <v>-172</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -14029,16 +13957,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I11" t="n">
-        <v>-167</v>
+        <v>-158</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -14065,39 +13993,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA@LV</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyren Williams</t>
+          <t>Ja'Marr Chase</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rec_yds</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>82.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="I12" t="n">
-        <v>-161</v>
+        <v>-156</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -14106,7 +14034,11 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14138,13 +14070,13 @@
         <v>15.5</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>0.61</v>
       </c>
       <c r="I13" t="n">
-        <v>-157</v>
+        <v>-154</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -14167,39 +14099,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Amon-Ra St. Brown</t>
+          <t>Noah Gray</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>84.5</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I14" t="n">
-        <v>-157</v>
+        <v>-153</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14218,12 +14150,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ja'Marr Chase</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14237,20 +14169,20 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I15" t="n">
-        <v>-156</v>
+        <v>-151</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14261,7 +14193,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
         </is>
       </c>
     </row>
@@ -14273,12 +14205,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Noah Gray</t>
+          <t>Courtland Sutton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -14288,24 +14220,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="I16" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -14319,44 +14251,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Kenneth Walker III</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>80.5</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-150</v>
+        <v>-130</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -14365,31 +14297,27 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>PLAY (thin)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Trey McBride</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rec</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -14398,20 +14326,20 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17.5</v>
+        <v>6.5</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-145</v>
+        <v>-129</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -14425,22 +14353,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>PLAY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NYG@HOU</t>
+          <t>DEN@ARI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Marvin Harrison Jr.</t>
+          <t>Bo Nix</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -14449,20 +14377,20 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-141</v>
+        <v>-128</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>6/6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -14471,11 +14399,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14485,12 +14409,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Courtland Sutton</t>
+          <t>Carnell Tate</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -14500,24 +14424,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-138</v>
+        <v>-127</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -14536,17 +14460,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PIT@NO</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aaron Rodgers</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pass_cmp</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -14555,20 +14479,20 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>21.5</v>
+        <v>180.5</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-136</v>
+        <v>-126</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -14582,22 +14506,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jameson Williams</t>
+          <t>Saquon Barkley</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -14606,20 +14530,20 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>54.5</v>
+        <v>70.5</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.65</v>
+        <v>0.92</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="I22" t="n">
-        <v>-134</v>
+        <v>-245</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -14627,23 +14551,31 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kenneth Walker III</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -14653,24 +14585,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>80.5</v>
+        <v>29.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.64</v>
+        <v>0.84</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="I23" t="n">
-        <v>-132</v>
+        <v>-204</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -14678,50 +14610,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>model vs own record</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>John Metchie III</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>rec_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10.5</v>
+        <v>74.5</v>
       </c>
       <c r="G24" s="6" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="H24" s="6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H24" s="6" t="n">
-        <v>0.57</v>
-      </c>
       <c r="I24" t="n">
-        <v>-131</v>
+        <v>-180</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -14729,54 +14665,54 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>MIA@NYJ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trey McBride</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6.5</v>
+        <v>17.5</v>
       </c>
       <c r="G25" s="6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H25" s="6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H25" s="6" t="n">
-        <v>0.57</v>
-      </c>
       <c r="I25" t="n">
-        <v>-131</v>
+        <v>-175</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -14784,13 +14720,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLAY</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -14800,7 +14740,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bo Nix</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -14810,24 +14750,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="I26" t="n">
-        <v>-130</v>
+        <v>-175</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -14835,28 +14775,32 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLAY (thin)</t>
+          <t>LEAN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IND@MIN</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>rec</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -14865,20 +14809,20 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.61</v>
+        <v>0.77</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="I27" t="n">
-        <v>-125</v>
+        <v>-175</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -14886,8 +14830,16 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -14897,17 +14849,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saquon Barkley</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -14916,20 +14868,20 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>70.5</v>
+        <v>5.5</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="I28" t="n">
-        <v>-244</v>
+        <v>-171</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -14937,14 +14889,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>fill-in QB (Tanner McKee)</t>
+          <t>fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
@@ -14961,12 +14909,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Deshaun Watson</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14975,20 +14923,20 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>29.5</v>
+        <v>14.5</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="I29" t="n">
-        <v>-207</v>
+        <v>-167</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -14998,7 +14946,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>same bet as sibling line</t>
+          <t>red-team downgrade</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -15011,39 +14959,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Tyler Huntley</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>16.5</v>
+        <v>197.5</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="I30" t="n">
-        <v>-175</v>
+        <v>-160</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -15051,14 +14999,10 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+          <t>fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
@@ -15070,17 +15014,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Michael Penix Jr.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_att</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -15089,20 +15033,20 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5.5</v>
+        <v>31.5</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="I31" t="n">
-        <v>-174</v>
+        <v>-157</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -15110,12 +15054,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>fill-in QB (QB1 Out)</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15125,12 +15069,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DEN@ARI</t>
+          <t>KC@SEA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15144,20 +15088,20 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I32" t="n">
-        <v>-173</v>
+        <v>-155</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -15180,12 +15124,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15199,20 +15143,20 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="I33" t="n">
-        <v>-168</v>
+        <v>-151</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -15235,39 +15179,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tyler Huntley</t>
+          <t>Dak Prescott</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pass_yds</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>197.5</v>
+        <v>9.5</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I34" t="n">
-        <v>-160</v>
+        <v>-151</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -15275,10 +15219,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>fill-in QB (QB1 Out)</t>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
@@ -15290,17 +15238,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Michael Penix Jr.</t>
+          <t>Javonte Williams</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pass_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -15309,20 +15257,20 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>31.5</v>
+        <v>64.5</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I35" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -15335,7 +15283,11 @@
           <t>same bet as sibling line</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15345,12 +15297,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>GB@DET</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Javonte Williams</t>
+          <t>Sione Vaki</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15360,24 +15312,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>65.5</v>
+        <v>8.5</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I36" t="n">
-        <v>-154</v>
+        <v>-149</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -15387,14 +15339,10 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15404,39 +15352,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KC@SEA</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Chuba Hubbard</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-154</v>
+        <v>-147</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -15444,12 +15392,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15459,12 +15407,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>NYG@HOU</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dak Prescott</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -15474,24 +15422,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>9.5</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I38" t="n">
-        <v>-153</v>
+        <v>-146</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15501,12 +15449,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>same bet as sibling line</t>
+          <t>red-team downgrade</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>opp QB: PHI fill-in QB (Tanner McKee)</t>
+          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
         </is>
       </c>
     </row>
@@ -15518,39 +15466,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SF@ATL</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brock Purdy</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>pass_cmp</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.5</v>
+        <v>19.5</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I39" t="n">
-        <v>-152</v>
+        <v>-146</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -15563,7 +15511,11 @@
           <t>same bet as sibling line</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>fill-in QB (Tanner McKee)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15578,12 +15530,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -15592,20 +15544,20 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>9.5</v>
+        <v>16.5</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I40" t="n">
-        <v>-151</v>
+        <v>-141</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>0/6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -15613,11 +15565,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>red-team downgrade</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
@@ -15632,39 +15580,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TB@CAR</t>
+          <t>CIN@BAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chuba Hubbard</t>
+          <t>Chase Brown</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>17.5</v>
+        <v>41.5</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I41" t="n">
-        <v>-146</v>
+        <v>-141</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -15672,10 +15620,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>same bet as sibling line</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
         </is>
       </c>
     </row>
@@ -15687,39 +15639,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GB@DET</t>
+          <t>LA@LV</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sione Vaki</t>
+          <t>Blake Corum</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F42" t="n">
         <v>8.5</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I42" t="n">
-        <v>-145</v>
+        <v>-139</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -15742,39 +15694,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DAL@PHI</t>
+          <t>CLE@TEN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tanner McKee</t>
+          <t>Quinshon Judkins</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>pass_cmp</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OVER</t>
+          <t>UNDER</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19.5</v>
+        <v>45.5</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I43" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1/1</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -15784,14 +15736,10 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
+          <t>red-team downgrade</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -15801,17 +15749,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CIN@BAL</t>
+          <t>DAL@PHI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Tanner McKee</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>pass_yds</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -15820,20 +15768,20 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>41.5</v>
+        <v>193.5</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I44" t="n">
-        <v>-145</v>
+        <v>-138</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -15848,7 +15796,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>opp QB: BAL fill-in QB (QB1 Out)</t>
+          <t>fill-in QB (Tanner McKee)</t>
         </is>
       </c>
     </row>
@@ -15860,17 +15808,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>SF@ATL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tony Pollard</t>
+          <t>Brock Purdy</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>rush_att</t>
+          <t>rush_yds</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -15879,20 +15827,20 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="I45" t="n">
-        <v>-145</v>
+        <v>-134</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -15902,7 +15850,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>red-team downgrade</t>
+          <t>same bet as sibling line</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
@@ -15915,39 +15863,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CLE@TEN</t>
+          <t>TB@CAR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>AJ Dillon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>rush_yds</t>
+          <t>rush_att</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UNDER</t>
+          <t>OVER</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>46.5</v>
+        <v>3.5</v>
       </c>
       <c r="G46" s="6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="I46" t="n">
-        <v>-142</v>
+        <v>-131</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3/5</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -15957,344 +15905,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NYG@HOU</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-141</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>DAL@PHI</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tanner McKee</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>pass_yds</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-140</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>fill-in QB (Tanner McKee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NYG@HOU</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-136</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>opp QB: NYG fill-in QB (J.J. McCarthy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>CLE@TEN</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tyjae Spears</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>OVER</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-136</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LA@LV</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>rush_att</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-136</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
           <t>red-team downgrade</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LEAN</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SF@ATL</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Brock Purdy</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>rush_yds</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>UNDER</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-135</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>same bet as sibling line</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>opp QB: TB QB1 designation (start probability 65%)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
